--- a/database/event/8047/event_8047_evp_summary.xlsx
+++ b/database/event/8047/event_8047_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8047" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8047" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>6.5102</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5178</v>
+        <v>3.9485</v>
       </c>
       <c r="E2" t="n">
         <v>10.817</v>
@@ -548,7 +548,7 @@
         <v>6.2487</v>
       </c>
       <c r="D3" t="n">
-        <v>3.357</v>
+        <v>3.7729</v>
       </c>
       <c r="E3" t="n">
         <v>10.3824</v>
@@ -594,7 +594,7 @@
         <v>3.6245</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7437</v>
+        <v>2.0115</v>
       </c>
       <c r="E4" t="n">
         <v>6.0223</v>
@@ -640,7 +640,7 @@
         <v>3.5385</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6908</v>
+        <v>1.9537</v>
       </c>
       <c r="E5" t="n">
         <v>5.8793</v>
@@ -686,7 +686,7 @@
         <v>3.4578</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6412</v>
+        <v>1.8996</v>
       </c>
       <c r="E6" t="n">
         <v>5.7452</v>
@@ -732,7 +732,7 @@
         <v>3.4452</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6335</v>
+        <v>1.8911</v>
       </c>
       <c r="E7" t="n">
         <v>5.7243</v>
@@ -778,7 +778,7 @@
         <v>3.2087</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4881</v>
+        <v>1.7324</v>
       </c>
       <c r="E8" t="n">
         <v>5.3314</v>
@@ -824,7 +824,7 @@
         <v>3.047</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3887</v>
+        <v>1.6239</v>
       </c>
       <c r="E9" t="n">
         <v>5.0627</v>
@@ -870,7 +870,7 @@
         <v>2.9873</v>
       </c>
       <c r="D10" t="n">
-        <v>1.352</v>
+        <v>1.5838</v>
       </c>
       <c r="E10" t="n">
         <v>4.9635</v>
@@ -916,7 +916,7 @@
         <v>2.8312</v>
       </c>
       <c r="D11" t="n">
-        <v>1.256</v>
+        <v>1.479</v>
       </c>
       <c r="E11" t="n">
         <v>4.7042</v>
@@ -962,7 +962,7 @@
         <v>2.7697</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2182</v>
+        <v>1.4377</v>
       </c>
       <c r="E12" t="n">
         <v>4.602</v>
@@ -1008,7 +1008,7 @@
         <v>2.7685</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2175</v>
+        <v>1.4369</v>
       </c>
       <c r="E13" t="n">
         <v>4.6</v>
@@ -1054,7 +1054,7 @@
         <v>2.6017</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1149</v>
+        <v>1.325</v>
       </c>
       <c r="E14" t="n">
         <v>4.3228</v>
@@ -1100,7 +1100,7 @@
         <v>2.5605</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0896</v>
+        <v>1.2973</v>
       </c>
       <c r="E15" t="n">
         <v>4.2543</v>
@@ -1146,7 +1146,7 @@
         <v>2.4714</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0348</v>
+        <v>1.2375</v>
       </c>
       <c r="E16" t="n">
         <v>4.1063</v>
@@ -1192,7 +1192,7 @@
         <v>2.4663</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0317</v>
+        <v>1.2341</v>
       </c>
       <c r="E17" t="n">
         <v>4.0978</v>
@@ -1238,7 +1238,7 @@
         <v>2.4266</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0073</v>
+        <v>1.2074</v>
       </c>
       <c r="E18" t="n">
         <v>4.0319</v>
@@ -1284,7 +1284,7 @@
         <v>2.4246</v>
       </c>
       <c r="D19" t="n">
-        <v>1.006</v>
+        <v>1.2061</v>
       </c>
       <c r="E19" t="n">
         <v>4.0285</v>
@@ -1330,7 +1330,7 @@
         <v>2.381</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9792</v>
+        <v>1.1768</v>
       </c>
       <c r="E20" t="n">
         <v>3.9561</v>
@@ -1376,7 +1376,7 @@
         <v>2.38</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9787</v>
+        <v>1.1762</v>
       </c>
       <c r="E21" t="n">
         <v>3.9545</v>
@@ -1422,7 +1422,7 @@
         <v>2.2926</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.1175</v>
       </c>
       <c r="E22" t="n">
         <v>3.8092</v>
@@ -1468,7 +1468,7 @@
         <v>2.2473</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8971</v>
+        <v>1.0871</v>
       </c>
       <c r="E23" t="n">
         <v>3.734</v>
@@ -1514,7 +1514,7 @@
         <v>2.2243</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8829</v>
+        <v>1.0717</v>
       </c>
       <c r="E24" t="n">
         <v>3.6958</v>
@@ -1560,7 +1560,7 @@
         <v>2.1845</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8585</v>
+        <v>1.045</v>
       </c>
       <c r="E25" t="n">
         <v>3.6297</v>
@@ -1606,7 +1606,7 @@
         <v>1.9942</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7415</v>
+        <v>0.9172</v>
       </c>
       <c r="E26" t="n">
         <v>3.3135</v>
@@ -1652,7 +1652,7 @@
         <v>1.965</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7235</v>
+        <v>0.8976</v>
       </c>
       <c r="E27" t="n">
         <v>3.265</v>
@@ -1698,7 +1698,7 @@
         <v>1.9595</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7201</v>
+        <v>0.8939</v>
       </c>
       <c r="E28" t="n">
         <v>3.2558</v>
@@ -1744,7 +1744,7 @@
         <v>1.7926</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6175</v>
+        <v>0.7819</v>
       </c>
       <c r="E29" t="n">
         <v>2.9785</v>
@@ -1790,7 +1790,7 @@
         <v>1.6326</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5192</v>
+        <v>0.6745</v>
       </c>
       <c r="E30" t="n">
         <v>2.7127</v>
@@ -1836,7 +1836,7 @@
         <v>1.508</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4426</v>
+        <v>0.5908</v>
       </c>
       <c r="E31" t="n">
         <v>2.5056</v>
@@ -1882,7 +1882,7 @@
         <v>1.3045</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3175</v>
+        <v>0.4543</v>
       </c>
       <c r="E32" t="n">
         <v>2.1675</v>
@@ -1928,7 +1928,7 @@
         <v>1.2871</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3067</v>
+        <v>0.4425</v>
       </c>
       <c r="E33" t="n">
         <v>2.1385</v>
@@ -1974,7 +1974,7 @@
         <v>1.2835</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3045</v>
+        <v>0.4402</v>
       </c>
       <c r="E34" t="n">
         <v>2.1326</v>
@@ -2020,7 +2020,7 @@
         <v>1.0303</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1489</v>
+        <v>0.2702</v>
       </c>
       <c r="E35" t="n">
         <v>1.7118</v>
@@ -2066,7 +2066,7 @@
         <v>0.9588</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1049</v>
+        <v>0.2222</v>
       </c>
       <c r="E36" t="n">
         <v>1.593</v>
@@ -2112,7 +2112,7 @@
         <v>0.9329</v>
       </c>
       <c r="D37" t="n">
-        <v>0.089</v>
+        <v>0.2048</v>
       </c>
       <c r="E37" t="n">
         <v>1.55</v>
@@ -2158,7 +2158,7 @@
         <v>0.9254</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0844</v>
+        <v>0.1998</v>
       </c>
       <c r="E38" t="n">
         <v>1.5376</v>
@@ -2204,7 +2204,7 @@
         <v>0.8381999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0308</v>
+        <v>0.1413</v>
       </c>
       <c r="E39" t="n">
         <v>1.3927</v>
@@ -2250,7 +2250,7 @@
         <v>0.6091</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1101</v>
+        <v>-0.0125</v>
       </c>
       <c r="E40" t="n">
         <v>1.012</v>
@@ -2296,7 +2296,7 @@
         <v>0.5702</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.134</v>
+        <v>-0.0386</v>
       </c>
       <c r="E41" t="n">
         <v>0.9474</v>
@@ -2342,7 +2342,7 @@
         <v>0.4856</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.186</v>
+        <v>-0.0954</v>
       </c>
       <c r="E42" t="n">
         <v>0.8069</v>
@@ -2388,7 +2388,7 @@
         <v>0.4797</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1896</v>
+        <v>-0.0994</v>
       </c>
       <c r="E43" t="n">
         <v>0.797</v>
@@ -2434,7 +2434,7 @@
         <v>0.4669</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1975</v>
+        <v>-0.108</v>
       </c>
       <c r="E44" t="n">
         <v>0.7758</v>
@@ -2480,7 +2480,7 @@
         <v>0.4626</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2001</v>
+        <v>-0.1108</v>
       </c>
       <c r="E45" t="n">
         <v>0.7687</v>
@@ -2526,7 +2526,7 @@
         <v>0.4595</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.202</v>
+        <v>-0.1129</v>
       </c>
       <c r="E46" t="n">
         <v>0.7635</v>
@@ -2572,7 +2572,7 @@
         <v>0.4081</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2336</v>
+        <v>-0.1474</v>
       </c>
       <c r="E47" t="n">
         <v>0.6781</v>
@@ -2618,7 +2618,7 @@
         <v>0.4049</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2356</v>
+        <v>-0.1496</v>
       </c>
       <c r="E48" t="n">
         <v>0.6727</v>
@@ -2664,7 +2664,7 @@
         <v>0.3112</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2932</v>
+        <v>-0.2125</v>
       </c>
       <c r="E49" t="n">
         <v>0.5171</v>
@@ -2710,7 +2710,7 @@
         <v>0.2844</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3097</v>
+        <v>-0.2305</v>
       </c>
       <c r="E50" t="n">
         <v>0.4725</v>
@@ -2756,7 +2756,7 @@
         <v>0.1991</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3621</v>
+        <v>-0.2877</v>
       </c>
       <c r="E51" t="n">
         <v>0.3308</v>
@@ -2802,7 +2802,7 @@
         <v>0.0624</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4462</v>
+        <v>-0.3795</v>
       </c>
       <c r="E52" t="n">
         <v>0.1036</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0984</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.545</v>
+        <v>-0.4874</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1635</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1594</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5825</v>
+        <v>-0.5284</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2649</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2141</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6162</v>
+        <v>-0.5651</v>
       </c>
       <c r="E55" t="n">
         <v>-0.3558</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2325</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6274</v>
+        <v>-0.5774</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3863</v>
@@ -3032,7 +3032,7 @@
         <v>-0.3038</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6713</v>
+        <v>-0.6252</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5047</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3106</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6754</v>
+        <v>-0.6298</v>
       </c>
       <c r="E58" t="n">
         <v>-0.516</v>
@@ -3124,7 +3124,7 @@
         <v>-0.3174</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6796</v>
+        <v>-0.6344</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5273</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3775</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7166</v>
+        <v>-0.6748</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6273</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3968</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7285</v>
+        <v>-0.6877</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6593</v>
@@ -3262,7 +3262,7 @@
         <v>-0.414</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.739</v>
+        <v>-0.6993</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6879</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4143</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7392</v>
+        <v>-0.6995</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6884</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5964</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8512</v>
+        <v>-0.8217</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9909</v>
@@ -3400,7 +3400,7 @@
         <v>-0.6916</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9097</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="E65" t="n">
         <v>-1.1491</v>
@@ -3446,7 +3446,7 @@
         <v>-0.7252</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9303</v>
+        <v>-0.9081</v>
       </c>
       <c r="E66" t="n">
         <v>-1.2049</v>
@@ -3492,7 +3492,7 @@
         <v>-0.737</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9376</v>
+        <v>-0.9161</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2246</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7554</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9489</v>
+        <v>-0.9284</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2551</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7857</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9675</v>
+        <v>-0.9487</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3054</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8714</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0202</v>
+        <v>-1.0063</v>
       </c>
       <c r="E70" t="n">
         <v>-1.4479</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8828</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0272</v>
+        <v>-1.0139</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4668</v>
@@ -3722,7 +3722,7 @@
         <v>-0.9077</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0426</v>
+        <v>-1.0306</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5082</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9107</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0444</v>
+        <v>-1.0327</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5132</v>
@@ -3814,7 +3814,7 @@
         <v>-1.0085</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1045</v>
+        <v>-1.0983</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6757</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0539</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1324</v>
+        <v>-1.1288</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7511</v>
@@ -3906,7 +3906,7 @@
         <v>-1.3776</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3315</v>
+        <v>-1.3461</v>
       </c>
       <c r="E76" t="n">
         <v>-2.289</v>
@@ -3952,7 +3952,7 @@
         <v>-1.4626</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3837</v>
+        <v>-1.4031</v>
       </c>
       <c r="E77" t="n">
         <v>-2.4302</v>
@@ -3998,7 +3998,7 @@
         <v>-1.4757</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3918</v>
+        <v>-1.4119</v>
       </c>
       <c r="E78" t="n">
         <v>-2.452</v>
@@ -4044,7 +4044,7 @@
         <v>-1.8056</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5945</v>
+        <v>-1.6333</v>
       </c>
       <c r="E79" t="n">
         <v>-3</v>
@@ -4090,7 +4090,7 @@
         <v>-2.3417</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9241</v>
+        <v>-1.9932</v>
       </c>
       <c r="E80" t="n">
         <v>-3.8908</v>
@@ -4136,7 +4136,7 @@
         <v>-2.5889</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.0761</v>
+        <v>-2.1591</v>
       </c>
       <c r="E81" t="n">
         <v>-4.3016</v>

--- a/database/event/8047/event_8047_evp_summary.xlsx
+++ b/database/event/8047/event_8047_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>6.5102</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9485</v>
+        <v>3.8656</v>
       </c>
       <c r="E2" t="n">
         <v>10.817</v>
@@ -548,7 +548,7 @@
         <v>6.2487</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7729</v>
+        <v>3.6924</v>
       </c>
       <c r="E3" t="n">
         <v>10.3824</v>
@@ -594,7 +594,7 @@
         <v>3.6245</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0115</v>
+        <v>1.9554</v>
       </c>
       <c r="E4" t="n">
         <v>6.0223</v>
@@ -640,7 +640,7 @@
         <v>3.5385</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9537</v>
+        <v>1.8984</v>
       </c>
       <c r="E5" t="n">
         <v>5.8793</v>
@@ -686,7 +686,7 @@
         <v>3.4578</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8996</v>
+        <v>1.845</v>
       </c>
       <c r="E6" t="n">
         <v>5.7452</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.7243</v>
+        <v>5.7116</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4452</v>
+        <v>3.4375</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8911</v>
+        <v>1.8316</v>
       </c>
       <c r="E7" t="n">
-        <v>5.7243</v>
+        <v>5.7116</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4049</v>
+        <v>3.3922</v>
       </c>
       <c r="G7" t="n">
         <v>2.3194</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4049</v>
+        <v>3.3922</v>
       </c>
       <c r="I7" t="n">
         <v>3.4208</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.3314</v>
+        <v>5.3189</v>
       </c>
       <c r="C8" t="n">
-        <v>3.2087</v>
+        <v>3.2012</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7324</v>
+        <v>1.6751</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3314</v>
+        <v>5.3189</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3505</v>
+        <v>3.338</v>
       </c>
       <c r="G8" t="n">
         <v>1.9809</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3505</v>
+        <v>3.338</v>
       </c>
       <c r="I8" t="n">
         <v>3.3661</v>
@@ -824,7 +824,7 @@
         <v>3.047</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6239</v>
+        <v>1.5731</v>
       </c>
       <c r="E9" t="n">
         <v>5.0627</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.9635</v>
+        <v>4.9479</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9873</v>
+        <v>2.9779</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5838</v>
+        <v>1.5273</v>
       </c>
       <c r="E10" t="n">
-        <v>4.9635</v>
+        <v>4.9479</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0993</v>
+        <v>2.0837</v>
       </c>
       <c r="G10" t="n">
         <v>2.8642</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0993</v>
+        <v>2.0837</v>
       </c>
       <c r="I10" t="n">
         <v>2.1189</v>
@@ -916,7 +916,7 @@
         <v>2.8312</v>
       </c>
       <c r="D11" t="n">
-        <v>1.479</v>
+        <v>1.4302</v>
       </c>
       <c r="E11" t="n">
         <v>4.7042</v>
@@ -962,7 +962,7 @@
         <v>2.7697</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4377</v>
+        <v>1.3895</v>
       </c>
       <c r="E12" t="n">
         <v>4.602</v>
@@ -1008,7 +1008,7 @@
         <v>2.7685</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4369</v>
+        <v>1.3887</v>
       </c>
       <c r="E13" t="n">
         <v>4.6</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.3228</v>
+        <v>4.3129</v>
       </c>
       <c r="C14" t="n">
-        <v>2.6017</v>
+        <v>2.5957</v>
       </c>
       <c r="D14" t="n">
-        <v>1.325</v>
+        <v>1.2743</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3228</v>
+        <v>4.3129</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1178</v>
+        <v>4.1079</v>
       </c>
       <c r="G14" t="n">
         <v>0.205</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1537</v>
+        <v>4.1382</v>
       </c>
       <c r="I14" t="n">
         <v>4.173</v>
@@ -1100,7 +1100,7 @@
         <v>2.5605</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2973</v>
+        <v>1.251</v>
       </c>
       <c r="E15" t="n">
         <v>4.2543</v>
@@ -1146,7 +1146,7 @@
         <v>2.4714</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2375</v>
+        <v>1.192</v>
       </c>
       <c r="E16" t="n">
         <v>4.1063</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.0978</v>
+        <v>4.089</v>
       </c>
       <c r="C17" t="n">
-        <v>2.4663</v>
+        <v>2.461</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2341</v>
+        <v>1.1851</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0978</v>
+        <v>4.089</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3522</v>
+        <v>2.3434</v>
       </c>
       <c r="G17" t="n">
         <v>1.7456</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3522</v>
+        <v>2.3434</v>
       </c>
       <c r="I17" t="n">
         <v>2.3631</v>
@@ -1238,7 +1238,7 @@
         <v>2.4266</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2074</v>
+        <v>1.1624</v>
       </c>
       <c r="E18" t="n">
         <v>4.0319</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.0285</v>
+        <v>4.0169</v>
       </c>
       <c r="C19" t="n">
-        <v>2.4246</v>
+        <v>2.4176</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2061</v>
+        <v>1.1564</v>
       </c>
       <c r="E19" t="n">
-        <v>4.0285</v>
+        <v>4.0169</v>
       </c>
       <c r="F19" t="n">
-        <v>4.5773</v>
+        <v>4.5657</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5488</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8742</v>
+        <v>4.856</v>
       </c>
       <c r="I19" t="n">
         <v>4.8969</v>
@@ -1330,7 +1330,7 @@
         <v>2.381</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1768</v>
+        <v>1.1322</v>
       </c>
       <c r="E20" t="n">
         <v>3.9561</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.9545</v>
+        <v>3.943</v>
       </c>
       <c r="C21" t="n">
-        <v>2.38</v>
+        <v>2.3731</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1762</v>
+        <v>1.127</v>
       </c>
       <c r="E21" t="n">
-        <v>3.9545</v>
+        <v>3.943</v>
       </c>
       <c r="F21" t="n">
-        <v>4.5516</v>
+        <v>4.5401</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5971</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8338</v>
+        <v>4.8158</v>
       </c>
       <c r="I21" t="n">
         <v>4.8563</v>
@@ -1422,7 +1422,7 @@
         <v>2.2926</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1175</v>
+        <v>1.0737</v>
       </c>
       <c r="E22" t="n">
         <v>3.8092</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.734</v>
+        <v>3.709</v>
       </c>
       <c r="C23" t="n">
-        <v>2.2473</v>
+        <v>2.2323</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0871</v>
+        <v>1.0338</v>
       </c>
       <c r="E23" t="n">
-        <v>3.734</v>
+        <v>3.709</v>
       </c>
       <c r="F23" t="n">
-        <v>3.3592</v>
+        <v>3.3342</v>
       </c>
       <c r="G23" t="n">
         <v>0.3748</v>
       </c>
       <c r="H23" t="n">
-        <v>3.3592</v>
+        <v>3.3342</v>
       </c>
       <c r="I23" t="n">
         <v>3.3905</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.6958</v>
+        <v>3.6743</v>
       </c>
       <c r="C24" t="n">
-        <v>2.2243</v>
+        <v>2.2114</v>
       </c>
       <c r="D24" t="n">
-        <v>1.0717</v>
+        <v>1.0199</v>
       </c>
       <c r="E24" t="n">
-        <v>3.6958</v>
+        <v>3.6743</v>
       </c>
       <c r="F24" t="n">
-        <v>4.3546</v>
+        <v>4.3331</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6588000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5249</v>
+        <v>4.4912</v>
       </c>
       <c r="I24" t="n">
         <v>4.5672</v>
@@ -1560,7 +1560,7 @@
         <v>2.1845</v>
       </c>
       <c r="D25" t="n">
-        <v>1.045</v>
+        <v>1.0022</v>
       </c>
       <c r="E25" t="n">
         <v>3.6297</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.3135</v>
+        <v>3.2919</v>
       </c>
       <c r="C26" t="n">
-        <v>1.9942</v>
+        <v>1.9812</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9172</v>
+        <v>0.8676</v>
       </c>
       <c r="E26" t="n">
-        <v>3.3135</v>
+        <v>3.2919</v>
       </c>
       <c r="F26" t="n">
-        <v>2.9072</v>
+        <v>2.8856</v>
       </c>
       <c r="G26" t="n">
         <v>0.4063</v>
       </c>
       <c r="H26" t="n">
-        <v>2.9072</v>
+        <v>2.8856</v>
       </c>
       <c r="I26" t="n">
         <v>2.9343</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.265</v>
+        <v>3.2425</v>
       </c>
       <c r="C27" t="n">
-        <v>1.965</v>
+        <v>1.9515</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8976</v>
+        <v>0.8479</v>
       </c>
       <c r="E27" t="n">
-        <v>3.265</v>
+        <v>3.2425</v>
       </c>
       <c r="F27" t="n">
-        <v>3.4117</v>
+        <v>3.5361</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1467</v>
+        <v>-0.2936</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4117</v>
+        <v>3.5361</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4435</v>
+        <v>3.5659</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1467</v>
+        <v>-0.2936</v>
       </c>
       <c r="K27" t="n">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="L27" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2968</v>
+        <v>3.2723</v>
       </c>
       <c r="N27" t="n">
-        <v>339</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.2558</v>
+        <v>3.2396</v>
       </c>
       <c r="C28" t="n">
-        <v>1.9595</v>
+        <v>1.9498</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8939</v>
+        <v>0.8467</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2558</v>
+        <v>3.2396</v>
       </c>
       <c r="F28" t="n">
-        <v>3.5494</v>
+        <v>3.3863</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2936</v>
+        <v>-0.1467</v>
       </c>
       <c r="H28" t="n">
-        <v>3.5494</v>
+        <v>3.3863</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5659</v>
+        <v>3.4435</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2936</v>
+        <v>-0.1467</v>
       </c>
       <c r="K28" t="n">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="L28" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2723</v>
+        <v>3.2968</v>
       </c>
       <c r="N28" t="n">
-        <v>317</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29">
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.9785</v>
+        <v>2.9554</v>
       </c>
       <c r="C29" t="n">
-        <v>1.7926</v>
+        <v>1.7787</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7819</v>
+        <v>0.7335</v>
       </c>
       <c r="E29" t="n">
-        <v>2.9785</v>
+        <v>2.9554</v>
       </c>
       <c r="F29" t="n">
-        <v>3.0998</v>
+        <v>3.0767</v>
       </c>
       <c r="G29" t="n">
         <v>-0.1213</v>
       </c>
       <c r="H29" t="n">
-        <v>3.0998</v>
+        <v>3.0767</v>
       </c>
       <c r="I29" t="n">
         <v>3.1287</v>
@@ -1790,7 +1790,7 @@
         <v>1.6326</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6745</v>
+        <v>0.6368</v>
       </c>
       <c r="E30" t="n">
         <v>2.7127</v>
@@ -1836,7 +1836,7 @@
         <v>1.508</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5908</v>
+        <v>0.5543</v>
       </c>
       <c r="E31" t="n">
         <v>2.5056</v>
@@ -1882,7 +1882,7 @@
         <v>1.3045</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4543</v>
+        <v>0.4196</v>
       </c>
       <c r="E32" t="n">
         <v>2.1675</v>
@@ -1928,7 +1928,7 @@
         <v>1.2871</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4425</v>
+        <v>0.4081</v>
       </c>
       <c r="E33" t="n">
         <v>2.1385</v>
@@ -1974,7 +1974,7 @@
         <v>1.2835</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4402</v>
+        <v>0.4057</v>
       </c>
       <c r="E34" t="n">
         <v>2.1326</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.7118</v>
+        <v>1.7027</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0303</v>
+        <v>1.0248</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2702</v>
+        <v>0.2344</v>
       </c>
       <c r="E35" t="n">
-        <v>1.7118</v>
+        <v>1.7027</v>
       </c>
       <c r="F35" t="n">
-        <v>2.44</v>
+        <v>2.4309</v>
       </c>
       <c r="G35" t="n">
         <v>-0.7282</v>
       </c>
       <c r="H35" t="n">
-        <v>2.44</v>
+        <v>2.4309</v>
       </c>
       <c r="I35" t="n">
         <v>2.4513</v>
@@ -2066,7 +2066,7 @@
         <v>0.9588</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2222</v>
+        <v>0.1907</v>
       </c>
       <c r="E36" t="n">
         <v>1.593</v>
@@ -2112,7 +2112,7 @@
         <v>0.9329</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2048</v>
+        <v>0.1736</v>
       </c>
       <c r="E37" t="n">
         <v>1.55</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.5376</v>
+        <v>1.5321</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9254</v>
+        <v>0.9221</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1998</v>
+        <v>0.1665</v>
       </c>
       <c r="E38" t="n">
-        <v>1.5376</v>
+        <v>1.5321</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4632</v>
+        <v>1.4577</v>
       </c>
       <c r="G38" t="n">
         <v>0.07439999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>1.4632</v>
+        <v>1.4577</v>
       </c>
       <c r="I38" t="n">
         <v>1.47</v>
@@ -2204,7 +2204,7 @@
         <v>0.8381999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1413</v>
+        <v>0.1109</v>
       </c>
       <c r="E39" t="n">
         <v>1.3927</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.012</v>
+        <v>1.0099</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6091</v>
+        <v>0.6078</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0125</v>
+        <v>-0.0416</v>
       </c>
       <c r="E40" t="n">
-        <v>1.012</v>
+        <v>1.0099</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5658</v>
+        <v>0.5637</v>
       </c>
       <c r="G40" t="n">
         <v>0.4462</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5658</v>
+        <v>0.5637</v>
       </c>
       <c r="I40" t="n">
         <v>0.5684</v>
@@ -2296,7 +2296,7 @@
         <v>0.5702</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0386</v>
+        <v>-0.0665</v>
       </c>
       <c r="E41" t="n">
         <v>0.9474</v>
@@ -2342,7 +2342,7 @@
         <v>0.4856</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0954</v>
+        <v>-0.1224</v>
       </c>
       <c r="E42" t="n">
         <v>0.8069</v>
@@ -2388,7 +2388,7 @@
         <v>0.4797</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0994</v>
+        <v>-0.1264</v>
       </c>
       <c r="E43" t="n">
         <v>0.797</v>
@@ -2434,7 +2434,7 @@
         <v>0.4669</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.108</v>
+        <v>-0.1348</v>
       </c>
       <c r="E44" t="n">
         <v>0.7758</v>
@@ -2480,7 +2480,7 @@
         <v>0.4626</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1108</v>
+        <v>-0.1377</v>
       </c>
       <c r="E45" t="n">
         <v>0.7687</v>
@@ -2526,7 +2526,7 @@
         <v>0.4595</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1129</v>
+        <v>-0.1397</v>
       </c>
       <c r="E46" t="n">
         <v>0.7635</v>
@@ -2572,7 +2572,7 @@
         <v>0.4081</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1474</v>
+        <v>-0.1738</v>
       </c>
       <c r="E47" t="n">
         <v>0.6781</v>
@@ -2618,7 +2618,7 @@
         <v>0.4049</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1496</v>
+        <v>-0.1759</v>
       </c>
       <c r="E48" t="n">
         <v>0.6727</v>
@@ -2664,7 +2664,7 @@
         <v>0.3112</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2125</v>
+        <v>-0.2379</v>
       </c>
       <c r="E49" t="n">
         <v>0.5171</v>
@@ -2710,7 +2710,7 @@
         <v>0.2844</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2305</v>
+        <v>-0.2557</v>
       </c>
       <c r="E50" t="n">
         <v>0.4725</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3308</v>
+        <v>0.3265</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1991</v>
+        <v>0.1965</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2877</v>
+        <v>-0.3138</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3308</v>
+        <v>0.3265</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5713</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G51" t="n">
         <v>-0.2405</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5713</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I51" t="n">
         <v>0.5766</v>
@@ -2802,7 +2802,7 @@
         <v>0.0624</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3795</v>
+        <v>-0.4026</v>
       </c>
       <c r="E52" t="n">
         <v>0.1036</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0984</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4874</v>
+        <v>-0.509</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1635</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1594</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5284</v>
+        <v>-0.5494</v>
       </c>
       <c r="E54" t="n">
         <v>-0.2649</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2141</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5651</v>
+        <v>-0.5857</v>
       </c>
       <c r="E55" t="n">
         <v>-0.3558</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2325</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5774</v>
+        <v>-0.5978</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3863</v>
@@ -3032,7 +3032,7 @@
         <v>-0.3038</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6252</v>
+        <v>-0.645</v>
       </c>
       <c r="E57" t="n">
         <v>-0.5047</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3106</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6298</v>
+        <v>-0.6495</v>
       </c>
       <c r="E58" t="n">
         <v>-0.516</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5273</v>
+        <v>-0.5346</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3174</v>
+        <v>-0.3218</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6344</v>
+        <v>-0.6569</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5273</v>
+        <v>-0.5346</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9816</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="G59" t="n">
         <v>-1.5089</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9816</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="I59" t="n">
         <v>0.9908</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3775</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6748</v>
+        <v>-0.6938</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6273</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6593</v>
+        <v>-0.6538</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3968</v>
+        <v>-0.3935</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6877</v>
+        <v>-0.7044</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6593</v>
+        <v>-0.6538</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7331</v>
+        <v>-0.7276</v>
       </c>
       <c r="G61" t="n">
         <v>0.0738</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7331</v>
+        <v>-0.7276</v>
       </c>
       <c r="I61" t="n">
         <v>-0.7399</v>
@@ -3262,7 +3262,7 @@
         <v>-0.414</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6993</v>
+        <v>-0.718</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6879</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6884</v>
+        <v>-0.6886</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4143</v>
+        <v>-0.4144</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6995</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6884</v>
+        <v>-0.6886</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0709</v>
+        <v>0.0707</v>
       </c>
       <c r="G63" t="n">
         <v>-0.7593</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0709</v>
+        <v>0.0707</v>
       </c>
       <c r="I63" t="n">
         <v>0.0713</v>
@@ -3354,7 +3354,7 @@
         <v>-0.5964</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8217</v>
+        <v>-0.8387</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9909</v>
@@ -3400,7 +3400,7 @@
         <v>-0.6916</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="E65" t="n">
         <v>-1.1491</v>
@@ -3446,7 +3446,7 @@
         <v>-0.7252</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9081</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>-1.2049</v>
@@ -3492,7 +3492,7 @@
         <v>-0.737</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9161</v>
+        <v>-0.9318</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2246</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7554</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9284</v>
+        <v>-0.9439</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2551</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7857</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9487</v>
+        <v>-0.964</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3054</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8714</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0063</v>
+        <v>-1.0208</v>
       </c>
       <c r="E70" t="n">
         <v>-1.4479</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8828</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0139</v>
+        <v>-1.0283</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4668</v>
@@ -3722,7 +3722,7 @@
         <v>-0.9077</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0306</v>
+        <v>-1.0448</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5082</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5132</v>
+        <v>-1.5107</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.9107</v>
+        <v>-0.9092</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0327</v>
+        <v>-1.0458</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5132</v>
+        <v>-1.5107</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.6796</v>
+        <v>-0.6771</v>
       </c>
       <c r="G73" t="n">
         <v>-0.8336</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6796</v>
+        <v>-0.6771</v>
       </c>
       <c r="I73" t="n">
         <v>-0.6828</v>
@@ -3814,7 +3814,7 @@
         <v>-1.0085</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0983</v>
+        <v>-1.1115</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6757</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0539</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1288</v>
+        <v>-1.1415</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7511</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2.289</v>
+        <v>-2.2796</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.3776</v>
+        <v>-1.372</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3461</v>
+        <v>-1.3521</v>
       </c>
       <c r="E76" t="n">
-        <v>-2.289</v>
+        <v>-2.2796</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.5266</v>
+        <v>-2.5172</v>
       </c>
       <c r="G76" t="n">
         <v>0.2376</v>
       </c>
       <c r="H76" t="n">
-        <v>-2.5266</v>
+        <v>-2.5172</v>
       </c>
       <c r="I76" t="n">
         <v>-2.5384</v>
@@ -3952,7 +3952,7 @@
         <v>-1.4626</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.4031</v>
+        <v>-1.4121</v>
       </c>
       <c r="E77" t="n">
         <v>-2.4302</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.452</v>
+        <v>-2.4449</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.4757</v>
+        <v>-1.4715</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4119</v>
+        <v>-1.418</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.452</v>
+        <v>-2.4449</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.9028</v>
+        <v>-1.8957</v>
       </c>
       <c r="G78" t="n">
         <v>-0.5492</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.9028</v>
+        <v>-1.8957</v>
       </c>
       <c r="I78" t="n">
         <v>-1.9117</v>
@@ -4044,7 +4044,7 @@
         <v>-1.8056</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6333</v>
+        <v>-1.6391</v>
       </c>
       <c r="E79" t="n">
         <v>-3</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.8908</v>
+        <v>-3.8798</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.3417</v>
+        <v>-2.3351</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9932</v>
+        <v>-1.9896</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.8908</v>
+        <v>-3.8798</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.9442</v>
+        <v>-2.9332</v>
       </c>
       <c r="G80" t="n">
         <v>-0.9466</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.9442</v>
+        <v>-2.9332</v>
       </c>
       <c r="I80" t="n">
         <v>-2.9579</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.3016</v>
+        <v>-4.2715</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.5889</v>
+        <v>-2.5708</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.1591</v>
+        <v>-2.1457</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.3016</v>
+        <v>-4.2715</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.0464</v>
+        <v>-4.0163</v>
       </c>
       <c r="G81" t="n">
         <v>-0.2552</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.0464</v>
+        <v>-4.0163</v>
       </c>
       <c r="I81" t="n">
         <v>-4.0842</v>

--- a/database/event/8047/event_8047_evp_summary.xlsx
+++ b/database/event/8047/event_8047_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.1402</v>
+        <v>10.4485</v>
       </c>
       <c r="C2" t="n">
-        <v>6.1029</v>
+        <v>6.2885</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9918</v>
+        <v>4.0533</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1402</v>
+        <v>10.4485</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5092</v>
+        <v>4.497</v>
       </c>
       <c r="G2" t="n">
-        <v>5.631</v>
+        <v>5.6171</v>
       </c>
       <c r="H2" t="n">
-        <v>7.1443</v>
+        <v>7.1175</v>
       </c>
       <c r="I2" t="n">
-        <v>7.1443</v>
+        <v>7.1175</v>
       </c>
       <c r="J2" t="n">
-        <v>5.631</v>
+        <v>5.6171</v>
       </c>
       <c r="K2" t="n">
         <v>162</v>
@@ -529,7 +529,7 @@
         <v>158</v>
       </c>
       <c r="M2" t="n">
-        <v>12.7753</v>
+        <v>12.7346</v>
       </c>
       <c r="N2" t="n">
         <v>320</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.442600000000001</v>
+        <v>9.6091</v>
       </c>
       <c r="C3" t="n">
-        <v>5.6831</v>
+        <v>5.7833</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6743</v>
+        <v>3.6784</v>
       </c>
       <c r="E3" t="n">
-        <v>9.442600000000001</v>
+        <v>9.6091</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2518</v>
+        <v>3.2521</v>
       </c>
       <c r="G3" t="n">
         <v>6.1908</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3923</v>
+        <v>4.3929</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3923</v>
+        <v>4.3929</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3958</v>
+        <v>6.3963</v>
       </c>
       <c r="K3" t="n">
         <v>162</v>
@@ -575,7 +575,7 @@
         <v>158</v>
       </c>
       <c r="M3" t="n">
-        <v>10.7881</v>
+        <v>10.7892</v>
       </c>
       <c r="N3" t="n">
         <v>320</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9504</v>
+        <v>6.207</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5813</v>
+        <v>3.7357</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0845</v>
+        <v>2.1587</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9504</v>
+        <v>6.207</v>
       </c>
       <c r="F4" t="n">
         <v>3.7558</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1947</v>
+        <v>2.1951</v>
       </c>
       <c r="H4" t="n">
         <v>5.4952</v>
@@ -612,7 +612,7 @@
         <v>5.6368</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1947</v>
+        <v>2.1951</v>
       </c>
       <c r="K4" t="n">
         <v>286</v>
@@ -621,7 +621,7 @@
         <v>107</v>
       </c>
       <c r="M4" t="n">
-        <v>7.8315</v>
+        <v>7.8319</v>
       </c>
       <c r="N4" t="n">
         <v>393</v>
@@ -630,265 +630,265 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2629</v>
+        <v>5.4356</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1675</v>
+        <v>3.2714</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7716</v>
+        <v>1.8141</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2629</v>
+        <v>5.4356</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0947</v>
+        <v>3.3141</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1682</v>
+        <v>1.9363</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0483</v>
+        <v>4.5285</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0483</v>
+        <v>4.6452</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1682</v>
+        <v>1.9363</v>
       </c>
       <c r="K5" t="n">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="L5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2165</v>
+        <v>6.5815</v>
       </c>
       <c r="N5" t="n">
-        <v>336</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2562</v>
+        <v>5.4</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1635</v>
+        <v>3.25</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7685</v>
+        <v>1.7982</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2562</v>
+        <v>5.4</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3073</v>
+        <v>3.1283</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9488</v>
+        <v>2.1685</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5138</v>
+        <v>4.122</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6301</v>
+        <v>4.122</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9488</v>
+        <v>2.1685</v>
       </c>
       <c r="K6" t="n">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="L6" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>6.5789</v>
+        <v>6.2905</v>
       </c>
       <c r="N6" t="n">
-        <v>393</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.0965</v>
+        <v>5.2772</v>
       </c>
       <c r="C7" t="n">
-        <v>3.0673</v>
+        <v>3.1761</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6958</v>
+        <v>1.7434</v>
       </c>
       <c r="E7" t="n">
-        <v>5.0965</v>
+        <v>5.2772</v>
       </c>
       <c r="F7" t="n">
-        <v>3.469</v>
+        <v>3.9857</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6275</v>
+        <v>0.9418</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8676</v>
+        <v>5.9985</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8676</v>
+        <v>5.9985</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6275</v>
+        <v>0.9418</v>
       </c>
       <c r="K7" t="n">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="L7" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="M7" t="n">
-        <v>6.495100000000001</v>
+        <v>6.9403</v>
       </c>
       <c r="N7" t="n">
-        <v>336</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0863</v>
+        <v>5.2132</v>
       </c>
       <c r="C8" t="n">
-        <v>3.0612</v>
+        <v>3.1376</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6912</v>
+        <v>1.7148</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0863</v>
+        <v>5.2132</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2847</v>
+        <v>3.4795</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8016</v>
+        <v>1.6148</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2847</v>
+        <v>4.8907</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2847</v>
+        <v>4.8907</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8016</v>
+        <v>1.6148</v>
       </c>
       <c r="K8" t="n">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="L8" t="n">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="M8" t="n">
-        <v>5.0863</v>
+        <v>6.5055</v>
       </c>
       <c r="N8" t="n">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.0598</v>
+        <v>5.2056</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0453</v>
+        <v>3.133</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6791</v>
+        <v>1.7114</v>
       </c>
       <c r="E9" t="n">
-        <v>5.0598</v>
+        <v>5.2056</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1567</v>
+        <v>1.2853</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9031</v>
+        <v>3.7826</v>
       </c>
       <c r="H9" t="n">
-        <v>4.184</v>
+        <v>1.2853</v>
       </c>
       <c r="I9" t="n">
-        <v>4.184</v>
+        <v>1.2853</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9031</v>
+        <v>3.7826</v>
       </c>
       <c r="K9" t="n">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="L9" t="n">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="M9" t="n">
-        <v>6.0871</v>
+        <v>5.0679</v>
       </c>
       <c r="N9" t="n">
-        <v>248</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.9278</v>
+        <v>5.1653</v>
       </c>
       <c r="C10" t="n">
-        <v>2.9658</v>
+        <v>3.1088</v>
       </c>
       <c r="D10" t="n">
-        <v>1.619</v>
+        <v>1.6934</v>
       </c>
       <c r="E10" t="n">
-        <v>4.9278</v>
+        <v>5.1653</v>
       </c>
       <c r="F10" t="n">
-        <v>3.986</v>
+        <v>3.1698</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9418</v>
+        <v>1.9031</v>
       </c>
       <c r="H10" t="n">
-        <v>5.9992</v>
+        <v>4.2128</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9992</v>
+        <v>4.2128</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9418</v>
+        <v>1.9031</v>
       </c>
       <c r="K10" t="n">
         <v>177</v>
@@ -897,7 +897,7 @@
         <v>71</v>
       </c>
       <c r="M10" t="n">
-        <v>6.941</v>
+        <v>6.1159</v>
       </c>
       <c r="N10" t="n">
         <v>248</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.6836</v>
+        <v>4.6595</v>
       </c>
       <c r="C11" t="n">
-        <v>2.8188</v>
+        <v>2.8043</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5079</v>
+        <v>1.4675</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6836</v>
+        <v>4.6595</v>
       </c>
       <c r="F11" t="n">
         <v>2.4047</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2789</v>
+        <v>2.2997</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5381</v>
+        <v>2.5383</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6706</v>
+        <v>2.6708</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2789</v>
+        <v>2.2997</v>
       </c>
       <c r="K11" t="n">
         <v>339</v>
@@ -943,7 +943,7 @@
         <v>187</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9495</v>
+        <v>4.970499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>526</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.2315</v>
+        <v>4.3158</v>
       </c>
       <c r="C12" t="n">
-        <v>2.5467</v>
+        <v>2.5975</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3021</v>
+        <v>1.314</v>
       </c>
       <c r="E12" t="n">
-        <v>4.2315</v>
+        <v>4.3158</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7201</v>
+        <v>4.1966</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5114</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2286</v>
+        <v>6.4602</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3118</v>
+        <v>6.4602</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5114</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="L12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8232</v>
+        <v>6.4602</v>
       </c>
       <c r="N12" t="n">
-        <v>393</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.193</v>
+        <v>4.2698</v>
       </c>
       <c r="C13" t="n">
-        <v>2.5236</v>
+        <v>2.5698</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2845</v>
+        <v>1.2934</v>
       </c>
       <c r="E13" t="n">
-        <v>4.193</v>
+        <v>4.2698</v>
       </c>
       <c r="F13" t="n">
-        <v>4.193</v>
+        <v>2.7146</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.5119</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4522</v>
+        <v>3.2166</v>
       </c>
       <c r="I13" t="n">
-        <v>6.4522</v>
+        <v>3.2994</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.5119</v>
       </c>
       <c r="K13" t="n">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M13" t="n">
-        <v>6.4522</v>
+        <v>4.8113</v>
       </c>
       <c r="N13" t="n">
-        <v>253</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.0305</v>
+        <v>4.2095</v>
       </c>
       <c r="C14" t="n">
-        <v>2.4258</v>
+        <v>2.5335</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2106</v>
+        <v>1.2665</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0305</v>
+        <v>4.2095</v>
       </c>
       <c r="F14" t="n">
-        <v>2.999</v>
+        <v>2.9929</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0315</v>
+        <v>1.0094</v>
       </c>
       <c r="H14" t="n">
-        <v>3.839</v>
+        <v>3.8256</v>
       </c>
       <c r="I14" t="n">
-        <v>3.839</v>
+        <v>3.8256</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0315</v>
+        <v>1.0094</v>
       </c>
       <c r="K14" t="n">
         <v>230</v>
@@ -1081,7 +1081,7 @@
         <v>106</v>
       </c>
       <c r="M14" t="n">
-        <v>4.8705</v>
+        <v>4.835</v>
       </c>
       <c r="N14" t="n">
         <v>336</v>
@@ -1090,415 +1090,415 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9386</v>
+        <v>4.1766</v>
       </c>
       <c r="C15" t="n">
-        <v>2.3705</v>
+        <v>2.5137</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1687</v>
+        <v>1.2518</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9386</v>
+        <v>4.1766</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2521</v>
+        <v>3.4977</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3135</v>
+        <v>0.3729</v>
       </c>
       <c r="H15" t="n">
-        <v>6.5815</v>
+        <v>4.9305</v>
       </c>
       <c r="I15" t="n">
-        <v>6.7511</v>
+        <v>5.1879</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3135</v>
+        <v>0.3729</v>
       </c>
       <c r="K15" t="n">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="M15" t="n">
-        <v>6.4376</v>
+        <v>5.5608</v>
       </c>
       <c r="N15" t="n">
-        <v>317</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.8707</v>
+        <v>4.0983</v>
       </c>
       <c r="C16" t="n">
-        <v>2.3296</v>
+        <v>2.4666</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1378</v>
+        <v>1.2168</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8707</v>
+        <v>4.0983</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4978</v>
+        <v>4.243</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3729</v>
+        <v>-0.3137</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9307</v>
+        <v>6.5616</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1881</v>
+        <v>6.7307</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3729</v>
+        <v>-0.3137</v>
       </c>
       <c r="K16" t="n">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="L16" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>5.561</v>
+        <v>6.417</v>
       </c>
       <c r="N16" t="n">
-        <v>339</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.8624</v>
+        <v>4.0221</v>
       </c>
       <c r="C17" t="n">
-        <v>2.3246</v>
+        <v>2.4207</v>
       </c>
       <c r="D17" t="n">
-        <v>1.134</v>
+        <v>1.1828</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8624</v>
+        <v>4.0221</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0481</v>
+        <v>3.8253</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8143</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9464</v>
+        <v>5.6474</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9464</v>
+        <v>5.6474</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8143</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>230</v>
+        <v>321</v>
       </c>
       <c r="L17" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7607</v>
+        <v>5.6474</v>
       </c>
       <c r="N17" t="n">
-        <v>336</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.8254</v>
+        <v>3.9921</v>
       </c>
       <c r="C18" t="n">
-        <v>2.3023</v>
+        <v>2.4027</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1172</v>
+        <v>1.1694</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8254</v>
+        <v>3.9921</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8254</v>
+        <v>3.5643</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6477</v>
+        <v>5.0763</v>
       </c>
       <c r="I18" t="n">
-        <v>5.6477</v>
+        <v>5.0763</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>321</v>
+        <v>202</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6477</v>
+        <v>5.0763</v>
       </c>
       <c r="N18" t="n">
-        <v>321</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.6992</v>
+        <v>3.9621</v>
       </c>
       <c r="C19" t="n">
-        <v>2.2264</v>
+        <v>2.3846</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0597</v>
+        <v>1.156</v>
       </c>
       <c r="E19" t="n">
-        <v>3.6992</v>
+        <v>3.9621</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6992</v>
+        <v>3.4692</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.1369</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3715</v>
+        <v>4.8681</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3715</v>
+        <v>4.9935</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.1369</v>
       </c>
       <c r="K19" t="n">
-        <v>321</v>
+        <v>283</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M19" t="n">
-        <v>5.3715</v>
+        <v>5.1304</v>
       </c>
       <c r="N19" t="n">
-        <v>321</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.6065</v>
+        <v>3.9343</v>
       </c>
       <c r="C20" t="n">
-        <v>2.1706</v>
+        <v>2.3679</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0175</v>
+        <v>1.1435</v>
       </c>
       <c r="E20" t="n">
-        <v>3.6065</v>
+        <v>3.9343</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4689</v>
+        <v>3.0476</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1376</v>
+        <v>0.8245</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8674</v>
+        <v>3.9454</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9928</v>
+        <v>3.9454</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1376</v>
+        <v>0.8245</v>
       </c>
       <c r="K20" t="n">
-        <v>283</v>
+        <v>230</v>
       </c>
       <c r="L20" t="n">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="M20" t="n">
-        <v>5.1304</v>
+        <v>4.7699</v>
       </c>
       <c r="N20" t="n">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.5646</v>
+        <v>3.7102</v>
       </c>
       <c r="C21" t="n">
-        <v>2.1454</v>
+        <v>2.233</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.0434</v>
       </c>
       <c r="E21" t="n">
-        <v>3.5646</v>
+        <v>3.7102</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5646</v>
+        <v>3.8077</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.3193</v>
       </c>
       <c r="H21" t="n">
-        <v>5.0768</v>
+        <v>5.6089</v>
       </c>
       <c r="I21" t="n">
-        <v>5.0768</v>
+        <v>5.7534</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.3193</v>
       </c>
       <c r="K21" t="n">
-        <v>202</v>
+        <v>283</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M21" t="n">
-        <v>5.0768</v>
+        <v>5.4341</v>
       </c>
       <c r="N21" t="n">
-        <v>202</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.4996</v>
+        <v>3.6949</v>
       </c>
       <c r="C22" t="n">
-        <v>2.1062</v>
+        <v>2.2238</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9689</v>
+        <v>1.0366</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4996</v>
+        <v>3.6949</v>
       </c>
       <c r="F22" t="n">
-        <v>4.0478</v>
+        <v>3.7032</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5482</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.1345</v>
+        <v>5.3803</v>
       </c>
       <c r="I22" t="n">
-        <v>6.1345</v>
+        <v>5.3803</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5482</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>177</v>
+        <v>321</v>
       </c>
       <c r="L22" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>5.5863</v>
+        <v>5.3803</v>
       </c>
       <c r="N22" t="n">
-        <v>248</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.4887</v>
+        <v>3.6763</v>
       </c>
       <c r="C23" t="n">
-        <v>2.0997</v>
+        <v>2.2126</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9639</v>
+        <v>1.0283</v>
       </c>
       <c r="E23" t="n">
-        <v>3.4887</v>
+        <v>3.6763</v>
       </c>
       <c r="F23" t="n">
-        <v>3.8076</v>
+        <v>4.0476</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3189</v>
+        <v>-0.5482</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6087</v>
+        <v>6.134</v>
       </c>
       <c r="I23" t="n">
-        <v>5.7532</v>
+        <v>6.134</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3189</v>
+        <v>-0.5482</v>
       </c>
       <c r="K23" t="n">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="L23" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>5.434299999999999</v>
+        <v>5.585800000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>345</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.4268</v>
+        <v>3.5369</v>
       </c>
       <c r="C24" t="n">
-        <v>2.0624</v>
+        <v>2.1287</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9357</v>
+        <v>0.966</v>
       </c>
       <c r="E24" t="n">
-        <v>3.4268</v>
+        <v>3.5369</v>
       </c>
       <c r="F24" t="n">
-        <v>3.4288</v>
+        <v>3.4292</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.002</v>
+        <v>-0.0022</v>
       </c>
       <c r="H24" t="n">
-        <v>4.7796</v>
+        <v>4.7804</v>
       </c>
       <c r="I24" t="n">
-        <v>4.9028</v>
+        <v>4.9036</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.002</v>
+        <v>-0.0022</v>
       </c>
       <c r="K24" t="n">
         <v>258</v>
@@ -1541,7 +1541,7 @@
         <v>59</v>
       </c>
       <c r="M24" t="n">
-        <v>4.9008</v>
+        <v>4.9014</v>
       </c>
       <c r="N24" t="n">
         <v>317</v>
@@ -1550,81 +1550,81 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.3245</v>
+        <v>3.3788</v>
       </c>
       <c r="C25" t="n">
-        <v>2.0009</v>
+        <v>2.0335</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8892</v>
+        <v>0.8954</v>
       </c>
       <c r="E25" t="n">
-        <v>3.3245</v>
+        <v>3.3788</v>
       </c>
       <c r="F25" t="n">
-        <v>3.3245</v>
+        <v>3.1396</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1381</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5513</v>
+        <v>4.1466</v>
       </c>
       <c r="I25" t="n">
-        <v>4.5513</v>
+        <v>4.3631</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.1381</v>
       </c>
       <c r="K25" t="n">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5513</v>
+        <v>4.5012</v>
       </c>
       <c r="N25" t="n">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.2708</v>
+        <v>3.3453</v>
       </c>
       <c r="C26" t="n">
-        <v>1.9685</v>
+        <v>2.0134</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8647</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>3.2708</v>
+        <v>3.3453</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1327</v>
+        <v>3.6025</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1381</v>
+        <v>-0.3887</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1316</v>
+        <v>5.1598</v>
       </c>
       <c r="I26" t="n">
-        <v>4.3473</v>
+        <v>5.4291</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1381</v>
+        <v>-0.3887</v>
       </c>
       <c r="K26" t="n">
         <v>295</v>
@@ -1633,7 +1633,7 @@
         <v>44</v>
       </c>
       <c r="M26" t="n">
-        <v>4.485399999999999</v>
+        <v>5.0404</v>
       </c>
       <c r="N26" t="n">
         <v>339</v>
@@ -1642,81 +1642,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.2661</v>
+        <v>3.3179</v>
       </c>
       <c r="C27" t="n">
-        <v>1.9657</v>
+        <v>1.9969</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8626</v>
+        <v>0.8682</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2661</v>
+        <v>3.3179</v>
       </c>
       <c r="F27" t="n">
-        <v>3.1694</v>
+        <v>3.1717</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09669999999999999</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2118</v>
+        <v>4.2169</v>
       </c>
       <c r="I27" t="n">
-        <v>4.4317</v>
+        <v>4.2169</v>
       </c>
       <c r="J27" t="n">
-        <v>0.09669999999999999</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>295</v>
+        <v>204</v>
       </c>
       <c r="L27" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5284</v>
+        <v>4.2169</v>
       </c>
       <c r="N27" t="n">
-        <v>339</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.2139</v>
+        <v>3.284</v>
       </c>
       <c r="C28" t="n">
-        <v>1.9343</v>
+        <v>1.9765</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8388</v>
+        <v>0.8531</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2139</v>
+        <v>3.284</v>
       </c>
       <c r="F28" t="n">
-        <v>3.6026</v>
+        <v>3.1693</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3887</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>5.1599</v>
+        <v>4.2116</v>
       </c>
       <c r="I28" t="n">
-        <v>5.4293</v>
+        <v>4.4315</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3887</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>295</v>
@@ -1725,7 +1725,7 @@
         <v>44</v>
       </c>
       <c r="M28" t="n">
-        <v>5.0406</v>
+        <v>4.5282</v>
       </c>
       <c r="N28" t="n">
         <v>339</v>
@@ -1734,599 +1734,599 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.1813</v>
+        <v>3.1337</v>
       </c>
       <c r="C29" t="n">
-        <v>1.9147</v>
+        <v>1.886</v>
       </c>
       <c r="D29" t="n">
-        <v>0.824</v>
+        <v>0.7859</v>
       </c>
       <c r="E29" t="n">
-        <v>3.1813</v>
+        <v>3.1337</v>
       </c>
       <c r="F29" t="n">
-        <v>3.1813</v>
+        <v>3.3242</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4.238</v>
+        <v>4.5508</v>
       </c>
       <c r="I29" t="n">
-        <v>4.238</v>
+        <v>4.5508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>204</v>
+        <v>321</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>4.238</v>
+        <v>4.5508</v>
       </c>
       <c r="N29" t="n">
-        <v>204</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.8092</v>
+        <v>2.8968</v>
       </c>
       <c r="C30" t="n">
-        <v>1.6907</v>
+        <v>1.7434</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6546</v>
+        <v>0.6801</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8092</v>
+        <v>2.8968</v>
       </c>
       <c r="F30" t="n">
-        <v>2.8092</v>
+        <v>2.8058</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4235</v>
+        <v>3.416</v>
       </c>
       <c r="I30" t="n">
-        <v>3.4235</v>
+        <v>3.416</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4235</v>
+        <v>3.416</v>
       </c>
       <c r="N30" t="n">
-        <v>202</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.799</v>
+        <v>2.8359</v>
       </c>
       <c r="C31" t="n">
-        <v>1.6846</v>
+        <v>1.7068</v>
       </c>
       <c r="D31" t="n">
-        <v>0.65</v>
+        <v>0.6529</v>
       </c>
       <c r="E31" t="n">
-        <v>2.799</v>
+        <v>2.8359</v>
       </c>
       <c r="F31" t="n">
-        <v>2.799</v>
+        <v>2.8225</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4011</v>
+        <v>3.4526</v>
       </c>
       <c r="I31" t="n">
-        <v>3.4011</v>
+        <v>3.4526</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4011</v>
+        <v>3.4526</v>
       </c>
       <c r="N31" t="n">
-        <v>253</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.6718</v>
+        <v>2.8359</v>
       </c>
       <c r="C32" t="n">
-        <v>1.608</v>
+        <v>1.7068</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5921</v>
+        <v>0.6529</v>
       </c>
       <c r="E32" t="n">
-        <v>2.6718</v>
+        <v>2.8359</v>
       </c>
       <c r="F32" t="n">
-        <v>2.6718</v>
+        <v>2.5855</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.1227</v>
+        <v>2.9339</v>
       </c>
       <c r="I32" t="n">
-        <v>3.1227</v>
+        <v>2.9339</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>321</v>
+        <v>216</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1227</v>
+        <v>2.9339</v>
       </c>
       <c r="N32" t="n">
-        <v>321</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ryu</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.6402</v>
+        <v>2.6729</v>
       </c>
       <c r="C33" t="n">
-        <v>1.589</v>
+        <v>1.6087</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5777</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>2.6402</v>
+        <v>2.6729</v>
       </c>
       <c r="F33" t="n">
-        <v>2.6402</v>
+        <v>2.5846</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="H33" t="n">
-        <v>3.0537</v>
+        <v>2.932</v>
       </c>
       <c r="I33" t="n">
-        <v>3.0537</v>
+        <v>3.0851</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="K33" t="n">
-        <v>202</v>
+        <v>339</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="M33" t="n">
-        <v>3.0537</v>
+        <v>3.1321</v>
       </c>
       <c r="N33" t="n">
-        <v>202</v>
+        <v>526</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>ryu</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.611</v>
+        <v>2.6103</v>
       </c>
       <c r="C34" t="n">
-        <v>1.5714</v>
+        <v>1.571</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5644</v>
+        <v>0.5521</v>
       </c>
       <c r="E34" t="n">
-        <v>2.611</v>
+        <v>2.6103</v>
       </c>
       <c r="F34" t="n">
-        <v>2.563</v>
+        <v>2.6402</v>
       </c>
       <c r="G34" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.8846</v>
+        <v>3.0536</v>
       </c>
       <c r="I34" t="n">
-        <v>3.0352</v>
+        <v>3.0536</v>
       </c>
       <c r="J34" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>339</v>
+        <v>202</v>
       </c>
       <c r="L34" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.0832</v>
+        <v>3.0536</v>
       </c>
       <c r="N34" t="n">
-        <v>526</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.5855</v>
+        <v>2.5176</v>
       </c>
       <c r="C35" t="n">
-        <v>1.5561</v>
+        <v>1.5152</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5528</v>
+        <v>0.5107</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5855</v>
+        <v>2.5176</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5855</v>
+        <v>2.2518</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.1927</v>
       </c>
       <c r="H35" t="n">
-        <v>2.9339</v>
+        <v>2.2518</v>
       </c>
       <c r="I35" t="n">
-        <v>2.9339</v>
+        <v>2.3098</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.1927</v>
       </c>
       <c r="K35" t="n">
-        <v>216</v>
+        <v>258</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M35" t="n">
-        <v>2.9339</v>
+        <v>2.5025</v>
       </c>
       <c r="N35" t="n">
-        <v>216</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.444</v>
+        <v>2.5067</v>
       </c>
       <c r="C36" t="n">
-        <v>1.4709</v>
+        <v>1.5087</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4884</v>
+        <v>0.5059</v>
       </c>
       <c r="E36" t="n">
-        <v>2.444</v>
+        <v>2.5067</v>
       </c>
       <c r="F36" t="n">
-        <v>2.2511</v>
+        <v>2.6717</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1929</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.2511</v>
+        <v>3.1225</v>
       </c>
       <c r="I36" t="n">
-        <v>2.3091</v>
+        <v>3.1225</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1929</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="L36" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.502</v>
+        <v>3.1225</v>
       </c>
       <c r="N36" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.3775</v>
+        <v>2.4361</v>
       </c>
       <c r="C37" t="n">
-        <v>1.4309</v>
+        <v>1.4662</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4581</v>
+        <v>0.4743</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3775</v>
+        <v>2.4361</v>
       </c>
       <c r="F37" t="n">
-        <v>2.4862</v>
+        <v>1.7583</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1087</v>
+        <v>0.5365</v>
       </c>
       <c r="H37" t="n">
-        <v>2.7165</v>
+        <v>1.7583</v>
       </c>
       <c r="I37" t="n">
-        <v>2.7165</v>
+        <v>1.8036</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1087</v>
+        <v>0.5365</v>
       </c>
       <c r="K37" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="L37" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="M37" t="n">
-        <v>2.6078</v>
+        <v>2.3401</v>
       </c>
       <c r="N37" t="n">
-        <v>336</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.2828</v>
+        <v>2.2243</v>
       </c>
       <c r="C38" t="n">
-        <v>1.3739</v>
+        <v>1.3387</v>
       </c>
       <c r="D38" t="n">
-        <v>0.415</v>
+        <v>0.3797</v>
       </c>
       <c r="E38" t="n">
-        <v>2.2828</v>
+        <v>2.2243</v>
       </c>
       <c r="F38" t="n">
-        <v>1.7454</v>
+        <v>2.0742</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5374</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.7454</v>
+        <v>2.0742</v>
       </c>
       <c r="I38" t="n">
-        <v>1.7904</v>
+        <v>2.0742</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5374</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>258</v>
+        <v>161</v>
       </c>
       <c r="L38" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.3278</v>
+        <v>2.0742</v>
       </c>
       <c r="N38" t="n">
-        <v>317</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.1906</v>
+        <v>2.2063</v>
       </c>
       <c r="C39" t="n">
-        <v>1.3184</v>
+        <v>1.3279</v>
       </c>
       <c r="D39" t="n">
-        <v>0.373</v>
+        <v>0.3717</v>
       </c>
       <c r="E39" t="n">
-        <v>2.1906</v>
+        <v>2.2063</v>
       </c>
       <c r="F39" t="n">
-        <v>1.9098</v>
+        <v>2.4671</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2808</v>
+        <v>-0.3548</v>
       </c>
       <c r="H39" t="n">
-        <v>1.9098</v>
+        <v>2.6749</v>
       </c>
       <c r="I39" t="n">
-        <v>1.9098</v>
+        <v>2.7438</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2808</v>
+        <v>-0.3548</v>
       </c>
       <c r="K39" t="n">
-        <v>162</v>
+        <v>283</v>
       </c>
       <c r="L39" t="n">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="M39" t="n">
-        <v>2.1906</v>
+        <v>2.389</v>
       </c>
       <c r="N39" t="n">
-        <v>320</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.0948</v>
+        <v>2.1868</v>
       </c>
       <c r="C40" t="n">
-        <v>1.2608</v>
+        <v>1.3161</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3294</v>
+        <v>0.363</v>
       </c>
       <c r="E40" t="n">
-        <v>2.0948</v>
+        <v>2.1868</v>
       </c>
       <c r="F40" t="n">
-        <v>2.4671</v>
+        <v>2.4821</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.3723</v>
+        <v>-0.1082</v>
       </c>
       <c r="H40" t="n">
-        <v>2.6748</v>
+        <v>2.7076</v>
       </c>
       <c r="I40" t="n">
-        <v>2.7437</v>
+        <v>2.7076</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3723</v>
+        <v>-0.1082</v>
       </c>
       <c r="K40" t="n">
-        <v>283</v>
+        <v>230</v>
       </c>
       <c r="L40" t="n">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="M40" t="n">
-        <v>2.3714</v>
+        <v>2.5994</v>
       </c>
       <c r="N40" t="n">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.0594</v>
+        <v>1.9412</v>
       </c>
       <c r="C41" t="n">
-        <v>1.2395</v>
+        <v>1.1683</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3133</v>
+        <v>0.2533</v>
       </c>
       <c r="E41" t="n">
-        <v>2.0594</v>
+        <v>1.9412</v>
       </c>
       <c r="F41" t="n">
-        <v>2.0594</v>
+        <v>1.9103</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="H41" t="n">
-        <v>2.0594</v>
+        <v>1.9103</v>
       </c>
       <c r="I41" t="n">
-        <v>2.0594</v>
+        <v>1.9103</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="K41" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M41" t="n">
-        <v>2.0594</v>
+        <v>2.1913</v>
       </c>
       <c r="N41" t="n">
-        <v>161</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42">
@@ -2336,28 +2336,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.8682</v>
+        <v>1.8233</v>
       </c>
       <c r="C42" t="n">
-        <v>1.1244</v>
+        <v>1.0974</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2262</v>
+        <v>0.2006</v>
       </c>
       <c r="E42" t="n">
-        <v>1.8682</v>
+        <v>1.8233</v>
       </c>
       <c r="F42" t="n">
-        <v>1.8682</v>
+        <v>1.8685</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.8682</v>
+        <v>1.8685</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8682</v>
+        <v>1.8685</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.8682</v>
+        <v>1.8685</v>
       </c>
       <c r="N42" t="n">
         <v>204</v>
@@ -2382,28 +2382,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.7468</v>
+        <v>1.7616</v>
       </c>
       <c r="C43" t="n">
-        <v>1.0513</v>
+        <v>1.0602</v>
       </c>
       <c r="D43" t="n">
-        <v>0.171</v>
+        <v>0.173</v>
       </c>
       <c r="E43" t="n">
-        <v>1.7468</v>
+        <v>1.7616</v>
       </c>
       <c r="F43" t="n">
-        <v>1.7468</v>
+        <v>1.7466</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.7468</v>
+        <v>1.7466</v>
       </c>
       <c r="I43" t="n">
-        <v>1.7468</v>
+        <v>1.7466</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7468</v>
+        <v>1.7466</v>
       </c>
       <c r="N43" t="n">
         <v>161</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.5194</v>
+        <v>1.5063</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9145</v>
+        <v>0.9066</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0675</v>
+        <v>0.059</v>
       </c>
       <c r="E44" t="n">
-        <v>1.5194</v>
+        <v>1.5063</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5194</v>
+        <v>1.5185</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5194</v>
+        <v>1.5185</v>
       </c>
       <c r="I44" t="n">
-        <v>1.5194</v>
+        <v>1.5185</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.5194</v>
+        <v>1.5185</v>
       </c>
       <c r="N44" t="n">
         <v>253</v>
@@ -2470,170 +2470,170 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.3554</v>
+        <v>1.331</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8158</v>
+        <v>0.8011</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0072</v>
+        <v>-0.0193</v>
       </c>
       <c r="E45" t="n">
-        <v>1.3554</v>
+        <v>1.331</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3554</v>
+        <v>1.0848</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.3554</v>
+        <v>1.0848</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3554</v>
+        <v>1.0848</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>216</v>
+        <v>154</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.3554</v>
+        <v>1.0848</v>
       </c>
       <c r="N45" t="n">
-        <v>216</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.3457</v>
+        <v>1.2995</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8099</v>
+        <v>0.7821</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0116</v>
+        <v>-0.0334</v>
       </c>
       <c r="E46" t="n">
-        <v>1.3457</v>
+        <v>1.2995</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3187</v>
+        <v>1.2964</v>
       </c>
       <c r="G46" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.3187</v>
+        <v>1.2964</v>
       </c>
       <c r="I46" t="n">
-        <v>1.3875</v>
+        <v>1.2964</v>
       </c>
       <c r="J46" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>339</v>
+        <v>204</v>
       </c>
       <c r="L46" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.4145</v>
+        <v>1.2964</v>
       </c>
       <c r="N46" t="n">
-        <v>526</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.2963</v>
+        <v>1.2889</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7802</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0341</v>
+        <v>-0.0381</v>
       </c>
       <c r="E47" t="n">
-        <v>1.2963</v>
+        <v>1.2889</v>
       </c>
       <c r="F47" t="n">
-        <v>1.2963</v>
+        <v>1.3093</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="H47" t="n">
-        <v>1.2963</v>
+        <v>1.3093</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2963</v>
+        <v>1.3777</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="K47" t="n">
-        <v>204</v>
+        <v>339</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="M47" t="n">
-        <v>1.2963</v>
+        <v>1.4157</v>
       </c>
       <c r="N47" t="n">
-        <v>204</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.142</v>
+        <v>1.1766</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6873</v>
+        <v>0.7081</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1043</v>
+        <v>-0.0883</v>
       </c>
       <c r="E48" t="n">
-        <v>1.142</v>
+        <v>1.1766</v>
       </c>
       <c r="F48" t="n">
-        <v>1.142</v>
+        <v>1.3554</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.142</v>
+        <v>1.3554</v>
       </c>
       <c r="I48" t="n">
-        <v>1.142</v>
+        <v>1.3554</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.142</v>
+        <v>1.3554</v>
       </c>
       <c r="N48" t="n">
         <v>216</v>
@@ -2654,32 +2654,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.1014</v>
+        <v>1.1555</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6629</v>
+        <v>0.6954</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1228</v>
+        <v>-0.0977</v>
       </c>
       <c r="E49" t="n">
-        <v>1.1014</v>
+        <v>1.1555</v>
       </c>
       <c r="F49" t="n">
-        <v>1.1014</v>
+        <v>1.142</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.1014</v>
+        <v>1.142</v>
       </c>
       <c r="I49" t="n">
-        <v>1.1014</v>
+        <v>1.142</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1014</v>
+        <v>1.142</v>
       </c>
       <c r="N49" t="n">
         <v>216</v>
@@ -2700,357 +2700,357 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.1007</v>
+        <v>1.1214</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6625</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1231</v>
+        <v>-0.1129</v>
       </c>
       <c r="E50" t="n">
-        <v>1.1007</v>
+        <v>1.1214</v>
       </c>
       <c r="F50" t="n">
-        <v>1.7568</v>
+        <v>1.1014</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.6561</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.7568</v>
+        <v>1.1014</v>
       </c>
       <c r="I50" t="n">
-        <v>1.7568</v>
+        <v>1.1014</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.6561</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="L50" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.1007</v>
+        <v>1.1014</v>
       </c>
       <c r="N50" t="n">
-        <v>248</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.0848</v>
+        <v>0.8844</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6529</v>
+        <v>0.5323</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1304</v>
+        <v>-0.2188</v>
       </c>
       <c r="E51" t="n">
-        <v>1.0848</v>
+        <v>0.8844</v>
       </c>
       <c r="F51" t="n">
-        <v>1.0848</v>
+        <v>0.8374</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.0848</v>
+        <v>0.8374</v>
       </c>
       <c r="I51" t="n">
-        <v>1.0848</v>
+        <v>0.8374</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1.0848</v>
+        <v>0.8374</v>
       </c>
       <c r="N51" t="n">
-        <v>154</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8509</v>
+        <v>0.8541</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5121</v>
+        <v>0.514</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2369</v>
+        <v>-0.2323</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8509</v>
+        <v>0.8541</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8509</v>
+        <v>0.8346</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8509</v>
+        <v>0.8346</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8509</v>
+        <v>0.8346</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>204</v>
+        <v>321</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8509</v>
+        <v>0.8346</v>
       </c>
       <c r="N52" t="n">
-        <v>204</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8436</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5077</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2402</v>
+        <v>-0.2416</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8436</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>1.0372</v>
+        <v>0.8726</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1936</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.0372</v>
+        <v>0.8726</v>
       </c>
       <c r="I53" t="n">
-        <v>1.064</v>
+        <v>0.8726</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.1936</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>286</v>
+        <v>204</v>
       </c>
       <c r="L53" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.8704000000000001</v>
+        <v>0.8726</v>
       </c>
       <c r="N53" t="n">
-        <v>393</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8374</v>
+        <v>0.8175</v>
       </c>
       <c r="C54" t="n">
-        <v>0.504</v>
+        <v>0.492</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.243</v>
+        <v>-0.2487</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8374</v>
+        <v>0.8175</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8374</v>
+        <v>1.7561</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.6561</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8374</v>
+        <v>1.7561</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8374</v>
+        <v>1.7561</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.6561</v>
       </c>
       <c r="K54" t="n">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8374</v>
+        <v>1.1</v>
       </c>
       <c r="N54" t="n">
-        <v>216</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8347</v>
+        <v>0.6474</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5024</v>
+        <v>0.3896</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.2442</v>
+        <v>-0.3246</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8347</v>
+        <v>0.6474</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8347</v>
+        <v>1.0372</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.2056</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8347</v>
+        <v>1.0372</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8347</v>
+        <v>1.064</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.2056</v>
       </c>
       <c r="K55" t="n">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8347</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>321</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4792</v>
+        <v>0.622</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2884</v>
+        <v>0.3744</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4061</v>
+        <v>-0.336</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4792</v>
+        <v>0.622</v>
       </c>
       <c r="F56" t="n">
-        <v>1.4664</v>
+        <v>0.343</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.9872</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.4664</v>
+        <v>0.343</v>
       </c>
       <c r="I56" t="n">
-        <v>1.543</v>
+        <v>0.343</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.9872</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>339</v>
+        <v>123</v>
       </c>
       <c r="L56" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5558</v>
+        <v>0.343</v>
       </c>
       <c r="N56" t="n">
-        <v>526</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4642</v>
+        <v>0.4584</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2794</v>
+        <v>0.2759</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4129</v>
+        <v>-0.4091</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4642</v>
+        <v>0.4584</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1977</v>
+        <v>1.4667</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2665</v>
+        <v>-0.9882</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1977</v>
+        <v>1.4667</v>
       </c>
       <c r="I57" t="n">
-        <v>0.208</v>
+        <v>1.5433</v>
       </c>
       <c r="J57" t="n">
-        <v>0.2665</v>
+        <v>-0.9882</v>
       </c>
       <c r="K57" t="n">
         <v>339</v>
@@ -3059,7 +3059,7 @@
         <v>187</v>
       </c>
       <c r="M57" t="n">
-        <v>0.4745</v>
+        <v>0.5550999999999999</v>
       </c>
       <c r="N57" t="n">
         <v>526</v>
@@ -3068,323 +3068,323 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.358</v>
+        <v>0.3253</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2155</v>
+        <v>0.1958</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4612</v>
+        <v>-0.4685</v>
       </c>
       <c r="E58" t="n">
-        <v>0.358</v>
+        <v>0.3253</v>
       </c>
       <c r="F58" t="n">
-        <v>0.358</v>
+        <v>0.2072</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.2659</v>
       </c>
       <c r="H58" t="n">
-        <v>0.358</v>
+        <v>0.2072</v>
       </c>
       <c r="I58" t="n">
-        <v>0.358</v>
+        <v>0.218</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.2659</v>
       </c>
       <c r="K58" t="n">
-        <v>123</v>
+        <v>339</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="M58" t="n">
-        <v>0.358</v>
+        <v>0.4839</v>
       </c>
       <c r="N58" t="n">
-        <v>123</v>
+        <v>526</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3542</v>
+        <v>0.2614</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2132</v>
+        <v>0.1573</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.463</v>
+        <v>-0.4971</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3542</v>
+        <v>0.2614</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.04</v>
+        <v>0.3582</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3942</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.04</v>
+        <v>0.3582</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.04</v>
+        <v>0.3582</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3942</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="L59" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.3542</v>
+        <v>0.3582</v>
       </c>
       <c r="N59" t="n">
-        <v>320</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3527</v>
+        <v>0.1234</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2123</v>
+        <v>0.0743</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.4636</v>
+        <v>-0.5587</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3527</v>
+        <v>0.1234</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3527</v>
+        <v>-0.0392</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.3947</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3527</v>
+        <v>-0.0392</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3527</v>
+        <v>-0.0392</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>0.3947</v>
       </c>
       <c r="K60" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3527</v>
+        <v>0.3555</v>
       </c>
       <c r="N60" t="n">
-        <v>123</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>vsm</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.082</v>
+        <v>0.0828</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0494</v>
+        <v>0.0498</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5869</v>
+        <v>-0.5768</v>
       </c>
       <c r="E61" t="n">
-        <v>0.082</v>
+        <v>0.0828</v>
       </c>
       <c r="F61" t="n">
-        <v>0.082</v>
+        <v>0.0378</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.082</v>
+        <v>0.0378</v>
       </c>
       <c r="I61" t="n">
-        <v>0.082</v>
+        <v>0.0378</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.082</v>
+        <v>0.0378</v>
       </c>
       <c r="N61" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vsm</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0378</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0228</v>
+        <v>-0.0494</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.607</v>
+        <v>-0.6505</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0378</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0378</v>
+        <v>0.0818</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0378</v>
+        <v>0.0818</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0378</v>
+        <v>0.0818</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0378</v>
+        <v>0.0818</v>
       </c>
       <c r="N62" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2374</v>
+        <v>-0.095</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1429</v>
+        <v>-0.0572</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7323</v>
+        <v>-0.6563</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2374</v>
+        <v>-0.095</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3253</v>
+        <v>-0.2834</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.5627</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.3253</v>
+        <v>-0.2834</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3337</v>
+        <v>-0.2834</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.5627</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>286</v>
+        <v>123</v>
       </c>
       <c r="L63" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.229</v>
+        <v>-0.2834</v>
       </c>
       <c r="N63" t="n">
-        <v>393</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2839</v>
+        <v>-0.3967</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1709</v>
+        <v>-0.2388</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7534</v>
+        <v>-0.791</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2839</v>
+        <v>-0.3967</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2839</v>
+        <v>0.3253</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-0.5622</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2839</v>
+        <v>0.3253</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2839</v>
+        <v>0.3337</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.5622</v>
       </c>
       <c r="K64" t="n">
-        <v>123</v>
+        <v>286</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2839</v>
+        <v>-0.2285</v>
       </c>
       <c r="N64" t="n">
-        <v>123</v>
+        <v>393</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.373</v>
+        <v>-0.5182</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2245</v>
+        <v>-0.3119</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.794</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.373</v>
+        <v>-0.5182</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.373</v>
+        <v>-0.3895</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.373</v>
+        <v>-0.3895</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.373</v>
+        <v>-0.3895</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.373</v>
+        <v>-0.3895</v>
       </c>
       <c r="N65" t="n">
         <v>204</v>
@@ -3436,78 +3436,78 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4788</v>
+        <v>-0.574</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2882</v>
+        <v>-0.3455</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8702</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4788</v>
+        <v>-0.574</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4788</v>
+        <v>-0.5589</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4788</v>
+        <v>-0.5589</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4788</v>
+        <v>-0.5589</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4788</v>
+        <v>-0.5589</v>
       </c>
       <c r="N66" t="n">
-        <v>202</v>
+        <v>253</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5584</v>
+        <v>-0.785</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3361</v>
+        <v>-0.4725</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8784</v>
+        <v>-0.9645</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5584</v>
+        <v>-0.785</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5584</v>
+        <v>-0.5914</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5584</v>
+        <v>-0.5914</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5584</v>
+        <v>-0.5914</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5584</v>
+        <v>-0.5914</v>
       </c>
       <c r="N67" t="n">
         <v>253</v>
@@ -3528,231 +3528,231 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5765</v>
+        <v>-0.7889</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.347</v>
+        <v>-0.4748</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5765</v>
+        <v>-0.7889</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5765</v>
+        <v>-0.4786</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5765</v>
+        <v>-0.4786</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5765</v>
+        <v>-0.4786</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5765</v>
+        <v>-0.4786</v>
       </c>
       <c r="N68" t="n">
-        <v>161</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.6001</v>
+        <v>-0.8135</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3612</v>
+        <v>-0.4896</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8974</v>
+        <v>-0.9772</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6001</v>
+        <v>-0.8135</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.6001</v>
+        <v>-0.5768</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.6001</v>
+        <v>-0.5768</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6001</v>
+        <v>-0.5768</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6001</v>
+        <v>-0.5768</v>
       </c>
       <c r="N69" t="n">
-        <v>253</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Chr1zN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6715</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4041</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.004</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6715</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6715</v>
+        <v>-0.8632</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6715</v>
+        <v>-0.8632</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6715</v>
+        <v>-0.8632</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6715</v>
+        <v>-0.8632</v>
       </c>
       <c r="N70" t="n">
-        <v>123</v>
+        <v>161</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.791</v>
+        <v>-0.9431</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4761</v>
+        <v>-0.5676</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9843</v>
+        <v>-1.0351</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.791</v>
+        <v>-0.9431</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.0671</v>
+        <v>-0.6713</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2761</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.0671</v>
+        <v>-0.6713</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.0671</v>
+        <v>-0.6713</v>
       </c>
       <c r="J71" t="n">
-        <v>0.2761</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="L71" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.7909999999999999</v>
+        <v>-0.6713</v>
       </c>
       <c r="N71" t="n">
-        <v>248</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Chr1zN</t>
+          <t>piriajr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.8631</v>
+        <v>-0.9941</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5195</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0171</v>
+        <v>-1.0579</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.8631</v>
+        <v>-0.9941</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.8631</v>
+        <v>-0.9544</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.8631</v>
+        <v>-0.9544</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.8631</v>
+        <v>-0.9544</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.8631</v>
+        <v>-0.9544</v>
       </c>
       <c r="N72" t="n">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73">
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9188</v>
+        <v>-1.0099</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.553</v>
+        <v>-0.6078</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0425</v>
+        <v>-1.0649</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9188</v>
+        <v>-1.0099</v>
       </c>
       <c r="F73" t="n">
         <v>-0.9188</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>piriajr</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.9544</v>
+        <v>-1.1289</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5744</v>
+        <v>-0.6794</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0587</v>
+        <v>-1.1181</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.9544</v>
+        <v>-1.1289</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.9544</v>
+        <v>-1.0678</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>0.2761</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.9544</v>
+        <v>-1.0678</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.9544</v>
+        <v>-1.0678</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>0.2761</v>
       </c>
       <c r="K74" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.9544</v>
+        <v>-0.7917000000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>154</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.9846</v>
+        <v>-1.2835</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.5926</v>
+        <v>-0.7725</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0724</v>
+        <v>-1.1871</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9846</v>
+        <v>-1.2835</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.9846</v>
+        <v>-1.0046</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.9846</v>
+        <v>-1.0046</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.9846</v>
+        <v>-1.0046</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.9846</v>
+        <v>-1.0046</v>
       </c>
       <c r="N75" t="n">
         <v>202</v>
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.2263</v>
+        <v>-1.6915</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7381</v>
+        <v>-1.018</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1824</v>
+        <v>-1.3694</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.2263</v>
+        <v>-1.6915</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.8919</v>
+        <v>-0.9206</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.3344</v>
+        <v>-0.3248</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8919</v>
+        <v>-0.9206</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9149</v>
+        <v>-0.9443</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.3344</v>
+        <v>-0.3248</v>
       </c>
       <c r="K76" t="n">
         <v>258</v>
@@ -3933,7 +3933,7 @@
         <v>59</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.2493</v>
+        <v>-1.2691</v>
       </c>
       <c r="N76" t="n">
         <v>317</v>
@@ -3946,31 +3946,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5933</v>
+        <v>-1.869</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9589</v>
+        <v>-1.1249</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3495</v>
+        <v>-1.4487</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5933</v>
+        <v>-1.869</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.7937</v>
+        <v>-1.7935</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2004</v>
+        <v>0.1996</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.7937</v>
+        <v>-1.7935</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.8399</v>
+        <v>-1.8397</v>
       </c>
       <c r="J77" t="n">
-        <v>0.2004</v>
+        <v>0.1996</v>
       </c>
       <c r="K77" t="n">
         <v>283</v>
@@ -3979,7 +3979,7 @@
         <v>62</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.6395</v>
+        <v>-1.6401</v>
       </c>
       <c r="N77" t="n">
         <v>345</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.7662</v>
+        <v>-1.9863</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.063</v>
+        <v>-1.1955</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4282</v>
+        <v>-1.5011</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.7662</v>
+        <v>-1.9863</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.7662</v>
+        <v>-1.766</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.7662</v>
+        <v>-1.766</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.7662</v>
+        <v>-1.766</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.7662</v>
+        <v>-1.766</v>
       </c>
       <c r="N78" t="n">
         <v>123</v>
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.586</v>
+        <v>-2.7826</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.5564</v>
+        <v>-1.6747</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.8014</v>
+        <v>-1.8567</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.586</v>
+        <v>-2.7826</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.002</v>
+        <v>-2.0188</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.584</v>
+        <v>-0.5756</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.002</v>
+        <v>-2.0188</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.0536</v>
+        <v>-2.0708</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.584</v>
+        <v>-0.5756</v>
       </c>
       <c r="K79" t="n">
         <v>283</v>
@@ -4071,7 +4071,7 @@
         <v>62</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.6376</v>
+        <v>-2.6464</v>
       </c>
       <c r="N79" t="n">
         <v>345</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.7041</v>
+        <v>-3.0593</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6275</v>
+        <v>-1.8412</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8552</v>
+        <v>-1.9803</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.7041</v>
+        <v>-3.0593</v>
       </c>
       <c r="F80" t="n">
         <v>-2.7041</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.7647</v>
+        <v>-3.1379</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.6639</v>
+        <v>-1.8886</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8828</v>
+        <v>-2.0155</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.7647</v>
+        <v>-3.1379</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.6429</v>
+        <v>-2.643</v>
       </c>
       <c r="G81" t="n">
         <v>-0.1218</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.6429</v>
+        <v>-2.643</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.7809</v>
+        <v>-2.781</v>
       </c>
       <c r="J81" t="n">
         <v>-0.1218</v>
@@ -4163,7 +4163,7 @@
         <v>44</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.9027</v>
+        <v>-2.9028</v>
       </c>
       <c r="N81" t="n">
         <v>339</v>
@@ -4269,10 +4269,10 @@
         <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.184</v>
+        <v>0.1836</v>
       </c>
       <c r="J2" t="n">
-        <v>4.232</v>
+        <v>4.2228</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0944</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.1689</v>
+        <v>-2.1712</v>
       </c>
     </row>
     <row r="4">
@@ -4346,13 +4346,13 @@
         <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1181</v>
+        <v>-0.1066</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.7163</v>
+        <v>-2.4518</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1296</v>
+        <v>-0.1297</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.9808</v>
+        <v>-2.9831</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2455</v>
+        <v>-0.2457</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.6465</v>
+        <v>-5.6511</v>
       </c>
     </row>
     <row r="7">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0323</v>
+        <v>-0.0329</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5491</v>
+        <v>-0.5593</v>
       </c>
     </row>
     <row r="13">
@@ -4706,13 +4706,13 @@
         <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3033</v>
+        <v>-0.2941</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.1561</v>
+        <v>-4.9997</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>0.63</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3737</v>
+        <v>-0.3739</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.3529</v>
+        <v>-6.3563</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.53</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4615</v>
+        <v>-0.4618</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.8455</v>
+        <v>-7.8506</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.45</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.5321</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.0406</v>
+        <v>-9.0457</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.58</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2276</v>
+        <v>1.2279</v>
       </c>
       <c r="J17" t="n">
-        <v>20.8692</v>
+        <v>20.8743</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.53</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1412</v>
+        <v>1.1415</v>
       </c>
       <c r="J18" t="n">
-        <v>19.4004</v>
+        <v>19.4055</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.45</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0017</v>
+        <v>1.0018</v>
       </c>
       <c r="J19" t="n">
-        <v>17.0289</v>
+        <v>17.0306</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>1.33</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7805</v>
+        <v>0.7808</v>
       </c>
       <c r="J20" t="n">
-        <v>13.2685</v>
+        <v>13.2736</v>
       </c>
     </row>
     <row r="21">
@@ -5026,13 +5026,13 @@
         <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7805</v>
+        <v>0.7612</v>
       </c>
       <c r="J21" t="n">
-        <v>13.2685</v>
+        <v>12.9404</v>
       </c>
     </row>
     <row r="22">
@@ -5718,7 +5718,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5758,7 +5758,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6466,13 +6466,13 @@
         <v>29</v>
       </c>
       <c r="H57" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4726</v>
+        <v>0.4603</v>
       </c>
       <c r="J57" t="n">
-        <v>13.7054</v>
+        <v>13.3487</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.08</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2127</v>
+        <v>0.2131</v>
       </c>
       <c r="J58" t="n">
-        <v>6.1683</v>
+        <v>6.1799</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0029</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.84</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2117</v>
+        <v>-0.2115</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.1393</v>
+        <v>-6.1335</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.84</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2117</v>
+        <v>-0.2115</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.1393</v>
+        <v>-6.1335</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>2.37</v>
       </c>
       <c r="I62" t="n">
-        <v>1.9233</v>
+        <v>1.9237</v>
       </c>
       <c r="J62" t="n">
-        <v>30.7728</v>
+        <v>30.7792</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.45</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8462</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>13.5392</v>
+        <v>13.5408</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.39</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7647</v>
+        <v>0.7649</v>
       </c>
       <c r="J64" t="n">
-        <v>12.2352</v>
+        <v>12.2384</v>
       </c>
     </row>
     <row r="65">
@@ -6786,13 +6786,13 @@
         <v>16</v>
       </c>
       <c r="H65" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>11.1056</v>
+        <v>10.8784</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>1.26</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5752</v>
+        <v>0.5754</v>
       </c>
       <c r="J66" t="n">
-        <v>9.203200000000001</v>
+        <v>9.2064</v>
       </c>
     </row>
     <row r="67">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3369</v>
+        <v>0.3364</v>
       </c>
       <c r="J77" t="n">
-        <v>8.085599999999999</v>
+        <v>8.073600000000001</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3182</v>
+        <v>0.3177</v>
       </c>
       <c r="J78" t="n">
-        <v>7.6368</v>
+        <v>7.6248</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0961</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.3064</v>
+        <v>-2.3088</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.82</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2287</v>
+        <v>-0.2289</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.4888</v>
+        <v>-5.4936</v>
       </c>
     </row>
     <row r="81">
@@ -7426,13 +7426,13 @@
         <v>24</v>
       </c>
       <c r="H81" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2781</v>
+        <v>-0.2686</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.6744</v>
+        <v>-6.4464</v>
       </c>
     </row>
     <row r="82">
@@ -7869,10 +7869,10 @@
         <v>0.89</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.1071</v>
+        <v>-0.1077</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.7136</v>
+        <v>-1.7232</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>0.74</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2715</v>
+        <v>-0.2719</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.344</v>
+        <v>-4.3504</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.59</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4066</v>
+        <v>-0.4069</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.5056</v>
+        <v>-6.5104</v>
       </c>
     </row>
     <row r="95">
@@ -7986,13 +7986,13 @@
         <v>16</v>
       </c>
       <c r="H95" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4945</v>
+        <v>-0.4859</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.912</v>
+        <v>-7.7744</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.48</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5033</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.0528</v>
+        <v>-8.055999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -8666,13 +8666,13 @@
         <v>23</v>
       </c>
       <c r="H112" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3657</v>
+        <v>0.3835</v>
       </c>
       <c r="J112" t="n">
-        <v>8.411099999999999</v>
+        <v>8.820499999999999</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>1.02</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0861</v>
+        <v>0.0857</v>
       </c>
       <c r="J113" t="n">
-        <v>1.9803</v>
+        <v>1.9711</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.93</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1062</v>
+        <v>-0.1063</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.4426</v>
+        <v>-2.4449</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.79</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2547</v>
+        <v>-0.2549</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.8581</v>
+        <v>-5.8627</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.71</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3309</v>
+        <v>-0.3311</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.6107</v>
+        <v>-7.6153</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9143</v>
+        <v>0.9147</v>
       </c>
       <c r="J117" t="n">
-        <v>21.0289</v>
+        <v>21.0381</v>
       </c>
     </row>
     <row r="118">
@@ -8906,13 +8906,13 @@
         <v>23</v>
       </c>
       <c r="H118" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7147</v>
+        <v>0.7002</v>
       </c>
       <c r="J118" t="n">
-        <v>16.4381</v>
+        <v>16.1046</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1.15</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4306</v>
+        <v>0.4309</v>
       </c>
       <c r="J119" t="n">
-        <v>9.9038</v>
+        <v>9.9107</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4087</v>
+        <v>0.4089</v>
       </c>
       <c r="J120" t="n">
-        <v>9.4001</v>
+        <v>9.4047</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2688</v>
+        <v>-0.2685</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.1824</v>
+        <v>-6.1755</v>
       </c>
     </row>
     <row r="122">
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3801</v>
+        <v>0.3792</v>
       </c>
       <c r="J157" t="n">
-        <v>6.4617</v>
+        <v>6.4464</v>
       </c>
     </row>
     <row r="158">
@@ -10506,13 +10506,13 @@
         <v>17</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.2324</v>
+        <v>-0.2228</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.9508</v>
+        <v>-3.7876</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>0.72</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3063</v>
+        <v>-0.3065</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.2071</v>
+        <v>-5.2105</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.7</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3247</v>
+        <v>-0.3249</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.5199</v>
+        <v>-5.5233</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.52</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4854</v>
+        <v>-0.4856</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.251799999999999</v>
+        <v>-8.2552</v>
       </c>
     </row>
     <row r="162">
@@ -10666,13 +10666,13 @@
         <v>19</v>
       </c>
       <c r="H162" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="I162" t="n">
-        <v>1.135</v>
+        <v>1.1228</v>
       </c>
       <c r="J162" t="n">
-        <v>21.565</v>
+        <v>21.3332</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.5</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9484</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>18.0196</v>
+        <v>18.0329</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>1.17</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4644</v>
+        <v>0.4648</v>
       </c>
       <c r="J164" t="n">
-        <v>8.823600000000001</v>
+        <v>8.831200000000001</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>1.13</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3792</v>
+        <v>0.3799</v>
       </c>
       <c r="J165" t="n">
-        <v>7.2048</v>
+        <v>7.2181</v>
       </c>
     </row>
     <row r="166">
@@ -10826,13 +10826,13 @@
         <v>19</v>
       </c>
       <c r="H166" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6999</v>
+        <v>-0.7215</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.2981</v>
+        <v>-13.7085</v>
       </c>
     </row>
     <row r="167">
@@ -11669,10 +11669,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4648</v>
+        <v>0.4642</v>
       </c>
       <c r="J187" t="n">
-        <v>9.295999999999999</v>
+        <v>9.284000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -11706,13 +11706,13 @@
         <v>20</v>
       </c>
       <c r="H188" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1227</v>
+        <v>-0.111</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.454</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>0.77</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2662</v>
+        <v>-0.2664</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.324</v>
+        <v>-5.328</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.71</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3227</v>
+        <v>-0.3229</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.454</v>
+        <v>-6.458</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.54</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.475</v>
+        <v>-0.4752</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.5</v>
+        <v>-9.504</v>
       </c>
     </row>
     <row r="192">
@@ -12269,10 +12269,10 @@
         <v>1.84</v>
       </c>
       <c r="I202" t="n">
-        <v>1.5268</v>
+        <v>1.5273</v>
       </c>
       <c r="J202" t="n">
-        <v>30.536</v>
+        <v>30.546</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.6</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2212</v>
+        <v>1.2216</v>
       </c>
       <c r="J203" t="n">
-        <v>24.424</v>
+        <v>24.432</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.13</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3729</v>
+        <v>0.3732</v>
       </c>
       <c r="J204" t="n">
-        <v>7.458</v>
+        <v>7.464</v>
       </c>
     </row>
     <row r="205">
@@ -12386,13 +12386,13 @@
         <v>20</v>
       </c>
       <c r="H205" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I205" t="n">
-        <v>0.1859</v>
+        <v>0.156</v>
       </c>
       <c r="J205" t="n">
-        <v>3.718</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.78</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6837</v>
+        <v>-0.6834</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.674</v>
+        <v>-13.668</v>
       </c>
     </row>
     <row r="207">
@@ -12666,13 +12666,13 @@
         <v>22</v>
       </c>
       <c r="H212" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I212" t="n">
-        <v>1.468</v>
+        <v>1.4558</v>
       </c>
       <c r="J212" t="n">
-        <v>32.296</v>
+        <v>32.0276</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.28</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7086</v>
+        <v>0.7089</v>
       </c>
       <c r="J213" t="n">
-        <v>15.5892</v>
+        <v>15.5958</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>1.08</v>
       </c>
       <c r="I214" t="n">
-        <v>0.253</v>
+        <v>0.2533</v>
       </c>
       <c r="J214" t="n">
-        <v>5.566</v>
+        <v>5.5726</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>1.08</v>
       </c>
       <c r="I215" t="n">
-        <v>0.253</v>
+        <v>0.2533</v>
       </c>
       <c r="J215" t="n">
-        <v>5.566</v>
+        <v>5.5726</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.89</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4103</v>
+        <v>-0.4099</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.0266</v>
+        <v>-9.017799999999999</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.55</v>
       </c>
       <c r="I217" t="n">
-        <v>0.955</v>
+        <v>0.9543</v>
       </c>
       <c r="J217" t="n">
-        <v>21.01</v>
+        <v>20.9946</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.27</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5404</v>
+        <v>0.5399</v>
       </c>
       <c r="J218" t="n">
-        <v>11.8888</v>
+        <v>11.8778</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.06</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1653</v>
+        <v>0.1651</v>
       </c>
       <c r="J219" t="n">
-        <v>3.6366</v>
+        <v>3.6322</v>
       </c>
     </row>
     <row r="220">
@@ -12986,13 +12986,13 @@
         <v>22</v>
       </c>
       <c r="H220" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3871</v>
+        <v>-0.3782</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.5162</v>
+        <v>-8.320399999999999</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.64</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4049</v>
+        <v>-0.4051</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.9078</v>
+        <v>-8.9122</v>
       </c>
     </row>
     <row r="222">
@@ -17066,13 +17066,13 @@
         <v>16</v>
       </c>
       <c r="H322" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I322" t="n">
-        <v>0.8824</v>
+        <v>0.8736</v>
       </c>
       <c r="J322" t="n">
-        <v>14.1184</v>
+        <v>13.9776</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.54</v>
       </c>
       <c r="I323" t="n">
-        <v>0.6399</v>
+        <v>0.6401</v>
       </c>
       <c r="J323" t="n">
-        <v>10.2384</v>
+        <v>10.2416</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>1.39</v>
       </c>
       <c r="I324" t="n">
-        <v>0.4933</v>
+        <v>0.4934</v>
       </c>
       <c r="J324" t="n">
-        <v>7.8928</v>
+        <v>7.8944</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>1.21</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2964</v>
+        <v>0.2965</v>
       </c>
       <c r="J325" t="n">
-        <v>4.7424</v>
+        <v>4.744</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>1.04</v>
       </c>
       <c r="I326" t="n">
-        <v>0.0581</v>
+        <v>0.0583</v>
       </c>
       <c r="J326" t="n">
-        <v>0.9296</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="327">
@@ -17266,13 +17266,13 @@
         <v>16</v>
       </c>
       <c r="H327" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1077</v>
       </c>
       <c r="J327" t="n">
-        <v>-1.5312</v>
+        <v>-1.7232</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>0.72</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2986</v>
+        <v>-0.2984</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.7776</v>
+        <v>-4.7744</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>0.67</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3424</v>
+        <v>-0.3422</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.4784</v>
+        <v>-5.4752</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.64</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3688</v>
+        <v>-0.3686</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.9008</v>
+        <v>-5.8976</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.5</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4925</v>
+        <v>-0.4922</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.88</v>
+        <v>-7.8752</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.13</v>
       </c>
       <c r="I332" t="n">
-        <v>0.3386</v>
+        <v>0.338</v>
       </c>
       <c r="J332" t="n">
-        <v>6.772</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="333">
@@ -17506,13 +17506,13 @@
         <v>20</v>
       </c>
       <c r="H333" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2165</v>
+        <v>0.2375</v>
       </c>
       <c r="J333" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.95</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0776</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>-1.552</v>
+        <v>-1.556</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.8</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2414</v>
+        <v>-0.2416</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.828</v>
+        <v>-4.832</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.47</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5392</v>
+        <v>-0.5394</v>
       </c>
       <c r="J336" t="n">
-        <v>-10.784</v>
+        <v>-10.788</v>
       </c>
     </row>
     <row r="337">
@@ -19069,10 +19069,10 @@
         <v>1.84</v>
       </c>
       <c r="I372" t="n">
-        <v>1.5246</v>
+        <v>1.5241</v>
       </c>
       <c r="J372" t="n">
-        <v>32.0166</v>
+        <v>32.0061</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.22</v>
       </c>
       <c r="I373" t="n">
-        <v>0.5774</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="J373" t="n">
-        <v>12.1254</v>
+        <v>12.1191</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>1.16</v>
       </c>
       <c r="I374" t="n">
-        <v>0.4434</v>
+        <v>0.4431</v>
       </c>
       <c r="J374" t="n">
-        <v>9.311400000000001</v>
+        <v>9.305099999999999</v>
       </c>
     </row>
     <row r="375">
@@ -19186,13 +19186,13 @@
         <v>21</v>
       </c>
       <c r="H375" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I375" t="n">
-        <v>0.3716</v>
+        <v>0.3956</v>
       </c>
       <c r="J375" t="n">
-        <v>7.8036</v>
+        <v>8.307600000000001</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>1.1</v>
       </c>
       <c r="I376" t="n">
-        <v>0.2955</v>
+        <v>0.2952</v>
       </c>
       <c r="J376" t="n">
-        <v>6.2055</v>
+        <v>6.1992</v>
       </c>
     </row>
     <row r="377">
@@ -19469,10 +19469,10 @@
         <v>1.55</v>
       </c>
       <c r="I382" t="n">
-        <v>1.1777</v>
+        <v>1.1767</v>
       </c>
       <c r="J382" t="n">
-        <v>35.331</v>
+        <v>35.301</v>
       </c>
     </row>
     <row r="383">
@@ -19506,13 +19506,13 @@
         <v>30</v>
       </c>
       <c r="H383" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I383" t="n">
-        <v>0.8973</v>
+        <v>0.9157</v>
       </c>
       <c r="J383" t="n">
-        <v>26.919</v>
+        <v>27.471</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.07</v>
       </c>
       <c r="I384" t="n">
-        <v>0.2324</v>
+        <v>0.2317</v>
       </c>
       <c r="J384" t="n">
-        <v>6.972</v>
+        <v>6.951</v>
       </c>
     </row>
     <row r="385">
@@ -19586,13 +19586,13 @@
         <v>30</v>
       </c>
       <c r="H385" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.0895</v>
+        <v>-0.0304</v>
       </c>
       <c r="J385" t="n">
-        <v>-2.685</v>
+        <v>-0.912</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.91</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3493</v>
+        <v>-0.35</v>
       </c>
       <c r="J386" t="n">
-        <v>-10.479</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="387">
@@ -21469,10 +21469,10 @@
         <v>1.86</v>
       </c>
       <c r="I432" t="n">
-        <v>1.2863</v>
+        <v>1.287</v>
       </c>
       <c r="J432" t="n">
-        <v>30.8712</v>
+        <v>30.888</v>
       </c>
     </row>
     <row r="433">
@@ -21506,13 +21506,13 @@
         <v>24</v>
       </c>
       <c r="H433" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="I433" t="n">
-        <v>0.3776</v>
+        <v>0.3604</v>
       </c>
       <c r="J433" t="n">
-        <v>9.0624</v>
+        <v>8.6496</v>
       </c>
     </row>
     <row r="434">
@@ -21549,10 +21549,10 @@
         <v>0.78</v>
       </c>
       <c r="I434" t="n">
-        <v>-0.2739</v>
+        <v>-0.2737</v>
       </c>
       <c r="J434" t="n">
-        <v>-6.5736</v>
+        <v>-6.5688</v>
       </c>
     </row>
     <row r="435">
@@ -21589,10 +21589,10 @@
         <v>0.67</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.3767</v>
+        <v>-0.3766</v>
       </c>
       <c r="J435" t="n">
-        <v>-9.040800000000001</v>
+        <v>-9.038399999999999</v>
       </c>
     </row>
     <row r="436">
@@ -21629,10 +21629,10 @@
         <v>0.62</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.4213</v>
+        <v>-0.4211</v>
       </c>
       <c r="J436" t="n">
-        <v>-10.1112</v>
+        <v>-10.1064</v>
       </c>
     </row>
     <row r="437">
@@ -23066,13 +23066,13 @@
         <v>21</v>
       </c>
       <c r="H472" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I472" t="n">
-        <v>0.8023</v>
+        <v>0.8167</v>
       </c>
       <c r="J472" t="n">
-        <v>16.8483</v>
+        <v>17.1507</v>
       </c>
     </row>
     <row r="473">
@@ -23109,10 +23109,10 @@
         <v>1.33</v>
       </c>
       <c r="I473" t="n">
-        <v>0.6631</v>
+        <v>0.6624</v>
       </c>
       <c r="J473" t="n">
-        <v>13.9251</v>
+        <v>13.9104</v>
       </c>
     </row>
     <row r="474">
@@ -23149,10 +23149,10 @@
         <v>0.7</v>
       </c>
       <c r="I474" t="n">
-        <v>-0.3423</v>
+        <v>-0.3425</v>
       </c>
       <c r="J474" t="n">
-        <v>-7.1883</v>
+        <v>-7.1925</v>
       </c>
     </row>
     <row r="475">
@@ -23189,10 +23189,10 @@
         <v>0.67</v>
       </c>
       <c r="I475" t="n">
-        <v>-0.3698</v>
+        <v>-0.37</v>
       </c>
       <c r="J475" t="n">
-        <v>-7.7658</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="476">
@@ -23229,10 +23229,10 @@
         <v>0.59</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.441</v>
+        <v>-0.4412</v>
       </c>
       <c r="J476" t="n">
-        <v>-9.260999999999999</v>
+        <v>-9.2652</v>
       </c>
     </row>
     <row r="477">
@@ -23266,13 +23266,13 @@
         <v>21</v>
       </c>
       <c r="H477" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I477" t="n">
-        <v>1.2646</v>
+        <v>1.252</v>
       </c>
       <c r="J477" t="n">
-        <v>26.5566</v>
+        <v>26.292</v>
       </c>
     </row>
     <row r="478">
@@ -23309,10 +23309,10 @@
         <v>1.33</v>
       </c>
       <c r="I478" t="n">
-        <v>0.8018</v>
+        <v>0.8021</v>
       </c>
       <c r="J478" t="n">
-        <v>16.8378</v>
+        <v>16.8441</v>
       </c>
     </row>
     <row r="479">
@@ -23349,10 +23349,10 @@
         <v>1.27</v>
       </c>
       <c r="I479" t="n">
-        <v>0.6833</v>
+        <v>0.6835</v>
       </c>
       <c r="J479" t="n">
-        <v>14.3493</v>
+        <v>14.3535</v>
       </c>
     </row>
     <row r="480">
@@ -23389,10 +23389,10 @@
         <v>1.27</v>
       </c>
       <c r="I480" t="n">
-        <v>0.6833</v>
+        <v>0.6835</v>
       </c>
       <c r="J480" t="n">
-        <v>14.3493</v>
+        <v>14.3535</v>
       </c>
     </row>
     <row r="481">
@@ -23429,10 +23429,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.612</v>
       </c>
       <c r="J481" t="n">
-        <v>-12.8604</v>
+        <v>-12.852</v>
       </c>
     </row>
     <row r="482">
@@ -23866,13 +23866,13 @@
         <v>23</v>
       </c>
       <c r="H492" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I492" t="n">
-        <v>1.1377</v>
+        <v>1.128</v>
       </c>
       <c r="J492" t="n">
-        <v>26.1671</v>
+        <v>25.944</v>
       </c>
     </row>
     <row r="493">
@@ -23909,10 +23909,10 @@
         <v>1.13</v>
       </c>
       <c r="I493" t="n">
-        <v>0.3246</v>
+        <v>0.3251</v>
       </c>
       <c r="J493" t="n">
-        <v>7.4658</v>
+        <v>7.4773</v>
       </c>
     </row>
     <row r="494">
@@ -23949,10 +23949,10 @@
         <v>0.68</v>
       </c>
       <c r="I494" t="n">
-        <v>-0.3599</v>
+        <v>-0.3597</v>
       </c>
       <c r="J494" t="n">
-        <v>-8.277699999999999</v>
+        <v>-8.273099999999999</v>
       </c>
     </row>
     <row r="495">
@@ -23989,10 +23989,10 @@
         <v>0.65</v>
       </c>
       <c r="I495" t="n">
-        <v>-0.3871</v>
+        <v>-0.3869</v>
       </c>
       <c r="J495" t="n">
-        <v>-8.9033</v>
+        <v>-8.8987</v>
       </c>
     </row>
     <row r="496">
@@ -24029,10 +24029,10 @@
         <v>0.53</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.4923</v>
+        <v>-0.4921</v>
       </c>
       <c r="J496" t="n">
-        <v>-11.3229</v>
+        <v>-11.3183</v>
       </c>
     </row>
     <row r="497">
@@ -25666,13 +25666,13 @@
         <v>20</v>
       </c>
       <c r="H537" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="I537" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8612</v>
       </c>
       <c r="J537" t="n">
-        <v>16.644</v>
+        <v>17.224</v>
       </c>
     </row>
     <row r="538">
@@ -25709,10 +25709,10 @@
         <v>0.98</v>
       </c>
       <c r="I538" t="n">
-        <v>-0.032</v>
+        <v>-0.0325</v>
       </c>
       <c r="J538" t="n">
-        <v>-0.64</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="539">
@@ -25749,10 +25749,10 @@
         <v>0.91</v>
       </c>
       <c r="I539" t="n">
-        <v>-0.1263</v>
+        <v>-0.1266</v>
       </c>
       <c r="J539" t="n">
-        <v>-2.526</v>
+        <v>-2.532</v>
       </c>
     </row>
     <row r="540">
@@ -25789,10 +25789,10 @@
         <v>0.6</v>
       </c>
       <c r="I540" t="n">
-        <v>-0.4258</v>
+        <v>-0.4262</v>
       </c>
       <c r="J540" t="n">
-        <v>-8.516</v>
+        <v>-8.523999999999999</v>
       </c>
     </row>
     <row r="541">
@@ -25829,10 +25829,10 @@
         <v>0.46</v>
       </c>
       <c r="I541" t="n">
-        <v>-0.5468</v>
+        <v>-0.5472</v>
       </c>
       <c r="J541" t="n">
-        <v>-10.936</v>
+        <v>-10.944</v>
       </c>
     </row>
     <row r="542">
@@ -27469,10 +27469,10 @@
         <v>1.83</v>
       </c>
       <c r="I582" t="n">
-        <v>0.8993</v>
+        <v>0.8996</v>
       </c>
       <c r="J582" t="n">
-        <v>13.4895</v>
+        <v>13.494</v>
       </c>
     </row>
     <row r="583">
@@ -27509,10 +27509,10 @@
         <v>1.78</v>
       </c>
       <c r="I583" t="n">
-        <v>0.8547</v>
+        <v>0.8549</v>
       </c>
       <c r="J583" t="n">
-        <v>12.8205</v>
+        <v>12.8235</v>
       </c>
     </row>
     <row r="584">
@@ -27546,13 +27546,13 @@
         <v>15</v>
       </c>
       <c r="H584" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I584" t="n">
-        <v>0.4477</v>
+        <v>0.4372</v>
       </c>
       <c r="J584" t="n">
-        <v>6.7155</v>
+        <v>6.558</v>
       </c>
     </row>
     <row r="585">
@@ -27589,10 +27589,10 @@
         <v>1.3</v>
       </c>
       <c r="I585" t="n">
-        <v>0.3939</v>
+        <v>0.394</v>
       </c>
       <c r="J585" t="n">
-        <v>5.9085</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="586">
@@ -27629,10 +27629,10 @@
         <v>1.08</v>
       </c>
       <c r="I586" t="n">
-        <v>0.1177</v>
+        <v>0.1178</v>
       </c>
       <c r="J586" t="n">
-        <v>1.7655</v>
+        <v>1.767</v>
       </c>
     </row>
     <row r="587">
@@ -27866,13 +27866,13 @@
         <v>24</v>
       </c>
       <c r="H592" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I592" t="n">
-        <v>1.0888</v>
+        <v>1.0785</v>
       </c>
       <c r="J592" t="n">
-        <v>26.1312</v>
+        <v>25.884</v>
       </c>
     </row>
     <row r="593">
@@ -28026,13 +28026,13 @@
         <v>24</v>
       </c>
       <c r="H596" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I596" t="n">
-        <v>-0.3672</v>
+        <v>-0.3581</v>
       </c>
       <c r="J596" t="n">
-        <v>-8.812799999999999</v>
+        <v>-8.5944</v>
       </c>
     </row>
     <row r="597">
@@ -28069,10 +28069,10 @@
         <v>1.6</v>
       </c>
       <c r="I597" t="n">
-        <v>1.2352</v>
+        <v>1.2347</v>
       </c>
       <c r="J597" t="n">
-        <v>29.6448</v>
+        <v>29.6328</v>
       </c>
     </row>
     <row r="598">
@@ -28109,10 +28109,10 @@
         <v>1.34</v>
       </c>
       <c r="I598" t="n">
-        <v>0.8293</v>
+        <v>0.8289</v>
       </c>
       <c r="J598" t="n">
-        <v>19.9032</v>
+        <v>19.8936</v>
       </c>
     </row>
     <row r="599">
@@ -28149,10 +28149,10 @@
         <v>1.32</v>
       </c>
       <c r="I599" t="n">
-        <v>0.7897</v>
+        <v>0.7893</v>
       </c>
       <c r="J599" t="n">
-        <v>18.9528</v>
+        <v>18.9432</v>
       </c>
     </row>
     <row r="600">
@@ -28186,13 +28186,13 @@
         <v>24</v>
       </c>
       <c r="H600" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I600" t="n">
-        <v>-0.0367</v>
+        <v>0.0228</v>
       </c>
       <c r="J600" t="n">
-        <v>-0.8808</v>
+        <v>0.5472</v>
       </c>
     </row>
     <row r="601">
@@ -28229,10 +28229,10 @@
         <v>0.83</v>
       </c>
       <c r="I601" t="n">
-        <v>-0.5584</v>
+        <v>-0.5587</v>
       </c>
       <c r="J601" t="n">
-        <v>-13.4016</v>
+        <v>-13.4088</v>
       </c>
     </row>
     <row r="602">
@@ -28266,13 +28266,13 @@
         <v>22</v>
       </c>
       <c r="H602" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="I602" t="n">
-        <v>0.4695</v>
+        <v>0.4531</v>
       </c>
       <c r="J602" t="n">
-        <v>10.329</v>
+        <v>9.9682</v>
       </c>
     </row>
     <row r="603">
@@ -28309,10 +28309,10 @@
         <v>1.07</v>
       </c>
       <c r="I603" t="n">
-        <v>0.1929</v>
+        <v>0.1932</v>
       </c>
       <c r="J603" t="n">
-        <v>4.2438</v>
+        <v>4.2504</v>
       </c>
     </row>
     <row r="604">
@@ -28349,10 +28349,10 @@
         <v>1.06</v>
       </c>
       <c r="I604" t="n">
-        <v>0.1714</v>
+        <v>0.1717</v>
       </c>
       <c r="J604" t="n">
-        <v>3.7708</v>
+        <v>3.7774</v>
       </c>
     </row>
     <row r="605">
@@ -28389,10 +28389,10 @@
         <v>0.9</v>
       </c>
       <c r="I605" t="n">
-        <v>-0.1463</v>
+        <v>-0.1461</v>
       </c>
       <c r="J605" t="n">
-        <v>-3.2186</v>
+        <v>-3.2142</v>
       </c>
     </row>
     <row r="606">
@@ -28429,10 +28429,10 @@
         <v>0.71</v>
       </c>
       <c r="I606" t="n">
-        <v>-0.3377</v>
+        <v>-0.3376</v>
       </c>
       <c r="J606" t="n">
-        <v>-7.4294</v>
+        <v>-7.4272</v>
       </c>
     </row>
     <row r="607">
@@ -29266,13 +29266,13 @@
         <v>17</v>
       </c>
       <c r="H627" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I627" t="n">
-        <v>-0.0403</v>
+        <v>-0.0254</v>
       </c>
       <c r="J627" t="n">
-        <v>-0.6851</v>
+        <v>-0.4318</v>
       </c>
     </row>
     <row r="628">
@@ -29309,10 +29309,10 @@
         <v>0.9</v>
       </c>
       <c r="I628" t="n">
-        <v>-0.1194</v>
+        <v>-0.1197</v>
       </c>
       <c r="J628" t="n">
-        <v>-2.0298</v>
+        <v>-2.0349</v>
       </c>
     </row>
     <row r="629">
@@ -29349,10 +29349,10 @@
         <v>0.78</v>
       </c>
       <c r="I629" t="n">
-        <v>-0.2481</v>
+        <v>-0.2484</v>
       </c>
       <c r="J629" t="n">
-        <v>-4.2177</v>
+        <v>-4.2228</v>
       </c>
     </row>
     <row r="630">
@@ -29389,10 +29389,10 @@
         <v>0.53</v>
       </c>
       <c r="I630" t="n">
-        <v>-0.4727</v>
+        <v>-0.4729</v>
       </c>
       <c r="J630" t="n">
-        <v>-8.0359</v>
+        <v>-8.039300000000001</v>
       </c>
     </row>
     <row r="631">
@@ -29429,10 +29429,10 @@
         <v>0.53</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.4727</v>
+        <v>-0.4729</v>
       </c>
       <c r="J631" t="n">
-        <v>-8.0359</v>
+        <v>-8.039300000000001</v>
       </c>
     </row>
     <row r="632">
@@ -30466,13 +30466,13 @@
         <v>17</v>
       </c>
       <c r="H657" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I657" t="n">
-        <v>0.7441</v>
+        <v>0.7589</v>
       </c>
       <c r="J657" t="n">
-        <v>12.6497</v>
+        <v>12.9013</v>
       </c>
     </row>
     <row r="658">
@@ -30509,10 +30509,10 @@
         <v>0.97</v>
       </c>
       <c r="I658" t="n">
-        <v>-0.0505</v>
+        <v>-0.0508</v>
       </c>
       <c r="J658" t="n">
-        <v>-0.8585</v>
+        <v>-0.8636</v>
       </c>
     </row>
     <row r="659">
@@ -30549,10 +30549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I659" t="n">
-        <v>-0.0919</v>
+        <v>-0.0921</v>
       </c>
       <c r="J659" t="n">
-        <v>-1.5623</v>
+        <v>-1.5657</v>
       </c>
     </row>
     <row r="660">
@@ -30589,10 +30589,10 @@
         <v>0.85</v>
       </c>
       <c r="I660" t="n">
-        <v>-0.1921</v>
+        <v>-0.1923</v>
       </c>
       <c r="J660" t="n">
-        <v>-3.2657</v>
+        <v>-3.2691</v>
       </c>
     </row>
     <row r="661">
@@ -30629,10 +30629,10 @@
         <v>0.35</v>
       </c>
       <c r="I661" t="n">
-        <v>-0.6403</v>
+        <v>-0.6404</v>
       </c>
       <c r="J661" t="n">
-        <v>-10.8851</v>
+        <v>-10.8868</v>
       </c>
     </row>
     <row r="662">
@@ -33066,13 +33066,13 @@
         <v>22</v>
       </c>
       <c r="H722" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="I722" t="n">
-        <v>1.0314</v>
+        <v>1.0602</v>
       </c>
       <c r="J722" t="n">
-        <v>22.6908</v>
+        <v>23.3244</v>
       </c>
     </row>
     <row r="723">
@@ -33109,10 +33109,10 @@
         <v>1.27</v>
       </c>
       <c r="I723" t="n">
-        <v>0.6908</v>
+        <v>0.6901</v>
       </c>
       <c r="J723" t="n">
-        <v>15.1976</v>
+        <v>15.1822</v>
       </c>
     </row>
     <row r="724">
@@ -33149,10 +33149,10 @@
         <v>1.23</v>
       </c>
       <c r="I724" t="n">
-        <v>0.6078</v>
+        <v>0.6073</v>
       </c>
       <c r="J724" t="n">
-        <v>13.3716</v>
+        <v>13.3606</v>
       </c>
     </row>
     <row r="725">
@@ -33189,10 +33189,10 @@
         <v>1.1</v>
       </c>
       <c r="I725" t="n">
-        <v>0.3093</v>
+        <v>0.3086</v>
       </c>
       <c r="J725" t="n">
-        <v>6.8046</v>
+        <v>6.7892</v>
       </c>
     </row>
     <row r="726">
@@ -33229,10 +33229,10 @@
         <v>0.98</v>
       </c>
       <c r="I726" t="n">
-        <v>-0.1359</v>
+        <v>-0.1366</v>
       </c>
       <c r="J726" t="n">
-        <v>-2.9898</v>
+        <v>-3.0052</v>
       </c>
     </row>
     <row r="727">
@@ -33669,10 +33669,10 @@
         <v>1.44</v>
       </c>
       <c r="I737" t="n">
-        <v>0.5806</v>
+        <v>0.5802</v>
       </c>
       <c r="J737" t="n">
-        <v>13.9344</v>
+        <v>13.9248</v>
       </c>
     </row>
     <row r="738">
@@ -33706,13 +33706,13 @@
         <v>24</v>
       </c>
       <c r="H738" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I738" t="n">
-        <v>0.308</v>
+        <v>0.32</v>
       </c>
       <c r="J738" t="n">
-        <v>7.392</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="739">
@@ -33749,10 +33749,10 @@
         <v>0.98</v>
       </c>
       <c r="I739" t="n">
-        <v>-0.05</v>
+        <v>-0.0502</v>
       </c>
       <c r="J739" t="n">
-        <v>-1.2</v>
+        <v>-1.2048</v>
       </c>
     </row>
     <row r="740">
@@ -33789,10 +33789,10 @@
         <v>0.98</v>
       </c>
       <c r="I740" t="n">
-        <v>-0.05</v>
+        <v>-0.0502</v>
       </c>
       <c r="J740" t="n">
-        <v>-1.2</v>
+        <v>-1.2048</v>
       </c>
     </row>
     <row r="741">
@@ -33829,10 +33829,10 @@
         <v>0.89</v>
       </c>
       <c r="I741" t="n">
-        <v>-0.1666</v>
+        <v>-0.1668</v>
       </c>
       <c r="J741" t="n">
-        <v>-3.9984</v>
+        <v>-4.0032</v>
       </c>
     </row>
     <row r="742">
@@ -34469,10 +34469,10 @@
         <v>1.23</v>
       </c>
       <c r="I757" t="n">
-        <v>0.3946</v>
+        <v>0.3951</v>
       </c>
       <c r="J757" t="n">
-        <v>8.2866</v>
+        <v>8.2971</v>
       </c>
     </row>
     <row r="758">
@@ -34509,10 +34509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I758" t="n">
-        <v>-0.0946</v>
+        <v>-0.0944</v>
       </c>
       <c r="J758" t="n">
-        <v>-1.9866</v>
+        <v>-1.9824</v>
       </c>
     </row>
     <row r="759">
@@ -34549,10 +34549,10 @@
         <v>0.88</v>
       </c>
       <c r="I759" t="n">
-        <v>-0.1632</v>
+        <v>-0.1631</v>
       </c>
       <c r="J759" t="n">
-        <v>-3.4272</v>
+        <v>-3.4251</v>
       </c>
     </row>
     <row r="760">
@@ -34589,10 +34589,10 @@
         <v>0.8</v>
       </c>
       <c r="I760" t="n">
-        <v>-0.2459</v>
+        <v>-0.2457</v>
       </c>
       <c r="J760" t="n">
-        <v>-5.1639</v>
+        <v>-5.1597</v>
       </c>
     </row>
     <row r="761">
@@ -34626,13 +34626,13 @@
         <v>21</v>
       </c>
       <c r="H761" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I761" t="n">
-        <v>-0.2459</v>
+        <v>-0.2555</v>
       </c>
       <c r="J761" t="n">
-        <v>-5.1639</v>
+        <v>-5.3655</v>
       </c>
     </row>
     <row r="762">
@@ -35066,13 +35066,13 @@
         <v>17</v>
       </c>
       <c r="H772" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I772" t="n">
-        <v>0.6046</v>
+        <v>0.6197</v>
       </c>
       <c r="J772" t="n">
-        <v>10.2782</v>
+        <v>10.5349</v>
       </c>
     </row>
     <row r="773">
@@ -35109,10 +35109,10 @@
         <v>0.84</v>
       </c>
       <c r="I773" t="n">
-        <v>-0.1983</v>
+        <v>-0.1985</v>
       </c>
       <c r="J773" t="n">
-        <v>-3.3711</v>
+        <v>-3.3745</v>
       </c>
     </row>
     <row r="774">
@@ -35149,10 +35149,10 @@
         <v>0.83</v>
       </c>
       <c r="I774" t="n">
-        <v>-0.2081</v>
+        <v>-0.2084</v>
       </c>
       <c r="J774" t="n">
-        <v>-3.5377</v>
+        <v>-3.5428</v>
       </c>
     </row>
     <row r="775">
@@ -35186,13 +35186,13 @@
         <v>17</v>
       </c>
       <c r="H775" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I775" t="n">
-        <v>-0.3505</v>
+        <v>-0.3418</v>
       </c>
       <c r="J775" t="n">
-        <v>-5.9585</v>
+        <v>-5.8106</v>
       </c>
     </row>
     <row r="776">
@@ -35229,10 +35229,10 @@
         <v>0.59</v>
       </c>
       <c r="I776" t="n">
-        <v>-0.4314</v>
+        <v>-0.4318</v>
       </c>
       <c r="J776" t="n">
-        <v>-7.3338</v>
+        <v>-7.3406</v>
       </c>
     </row>
     <row r="777">
@@ -35269,10 +35269,10 @@
         <v>1.98</v>
       </c>
       <c r="I777" t="n">
-        <v>1.6633</v>
+        <v>1.6638</v>
       </c>
       <c r="J777" t="n">
-        <v>28.2761</v>
+        <v>28.2846</v>
       </c>
     </row>
     <row r="778">
@@ -35306,13 +35306,13 @@
         <v>17</v>
       </c>
       <c r="H778" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I778" t="n">
-        <v>1.1347</v>
+        <v>1.1221</v>
       </c>
       <c r="J778" t="n">
-        <v>19.2899</v>
+        <v>19.0757</v>
       </c>
     </row>
     <row r="779">
@@ -35349,10 +35349,10 @@
         <v>1.32</v>
       </c>
       <c r="I779" t="n">
-        <v>0.7649</v>
+        <v>0.7652</v>
       </c>
       <c r="J779" t="n">
-        <v>13.0033</v>
+        <v>13.0084</v>
       </c>
     </row>
     <row r="780">
@@ -35389,10 +35389,10 @@
         <v>1.21</v>
       </c>
       <c r="I780" t="n">
-        <v>0.5375</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J780" t="n">
-        <v>9.137499999999999</v>
+        <v>9.1426</v>
       </c>
     </row>
     <row r="781">
@@ -35429,10 +35429,10 @@
         <v>1.01</v>
       </c>
       <c r="I781" t="n">
-        <v>-0.0083</v>
+        <v>-0.008</v>
       </c>
       <c r="J781" t="n">
-        <v>-0.1411</v>
+        <v>-0.136</v>
       </c>
     </row>
     <row r="782">
@@ -35869,10 +35869,10 @@
         <v>1.09</v>
       </c>
       <c r="I792" t="n">
-        <v>0.2568</v>
+        <v>0.2573</v>
       </c>
       <c r="J792" t="n">
-        <v>5.136</v>
+        <v>5.146</v>
       </c>
     </row>
     <row r="793">
@@ -35909,10 +35909,10 @@
         <v>1.02</v>
       </c>
       <c r="I793" t="n">
-        <v>0.0922</v>
+        <v>0.0926</v>
       </c>
       <c r="J793" t="n">
-        <v>1.844</v>
+        <v>1.852</v>
       </c>
     </row>
     <row r="794">
@@ -35949,10 +35949,10 @@
         <v>0.88</v>
       </c>
       <c r="I794" t="n">
-        <v>-0.1604</v>
+        <v>-0.1602</v>
       </c>
       <c r="J794" t="n">
-        <v>-3.208</v>
+        <v>-3.204</v>
       </c>
     </row>
     <row r="795">
@@ -35989,10 +35989,10 @@
         <v>0.87</v>
       </c>
       <c r="I795" t="n">
-        <v>-0.1709</v>
+        <v>-0.1708</v>
       </c>
       <c r="J795" t="n">
-        <v>-3.418</v>
+        <v>-3.416</v>
       </c>
     </row>
     <row r="796">
@@ -36026,13 +36026,13 @@
         <v>20</v>
       </c>
       <c r="H796" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I796" t="n">
-        <v>-0.4276</v>
+        <v>-0.4362</v>
       </c>
       <c r="J796" t="n">
-        <v>-8.552</v>
+        <v>-8.724</v>
       </c>
     </row>
     <row r="797">
@@ -36509,10 +36509,10 @@
         <v>1.64</v>
       </c>
       <c r="I808" t="n">
-        <v>1.2297</v>
+        <v>1.2299</v>
       </c>
       <c r="J808" t="n">
-        <v>18.4455</v>
+        <v>18.4485</v>
       </c>
     </row>
     <row r="809">
@@ -36549,10 +36549,10 @@
         <v>1.63</v>
       </c>
       <c r="I809" t="n">
-        <v>1.2176</v>
+        <v>1.2178</v>
       </c>
       <c r="J809" t="n">
-        <v>18.264</v>
+        <v>18.267</v>
       </c>
     </row>
     <row r="810">
@@ -36589,10 +36589,10 @@
         <v>1.61</v>
       </c>
       <c r="I810" t="n">
-        <v>1.1934</v>
+        <v>1.1935</v>
       </c>
       <c r="J810" t="n">
-        <v>17.901</v>
+        <v>17.9025</v>
       </c>
     </row>
     <row r="811">
@@ -36626,13 +36626,13 @@
         <v>15</v>
       </c>
       <c r="H811" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="I811" t="n">
-        <v>-0.9528</v>
+        <v>-0.9728</v>
       </c>
       <c r="J811" t="n">
-        <v>-14.292</v>
+        <v>-14.592</v>
       </c>
     </row>
     <row r="812">
@@ -39869,10 +39869,10 @@
         <v>1.61</v>
       </c>
       <c r="I892" t="n">
-        <v>1.249</v>
+        <v>1.2494</v>
       </c>
       <c r="J892" t="n">
-        <v>26.229</v>
+        <v>26.2374</v>
       </c>
     </row>
     <row r="893">
@@ -39909,10 +39909,10 @@
         <v>1.54</v>
       </c>
       <c r="I893" t="n">
-        <v>1.1553</v>
+        <v>1.1557</v>
       </c>
       <c r="J893" t="n">
-        <v>24.2613</v>
+        <v>24.2697</v>
       </c>
     </row>
     <row r="894">
@@ -39946,13 +39946,13 @@
         <v>21</v>
       </c>
       <c r="H894" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="I894" t="n">
-        <v>1.059</v>
+        <v>1.0448</v>
       </c>
       <c r="J894" t="n">
-        <v>22.239</v>
+        <v>21.9408</v>
       </c>
     </row>
     <row r="895">
@@ -39989,10 +39989,10 @@
         <v>1.01</v>
       </c>
       <c r="I895" t="n">
-        <v>0.0235</v>
+        <v>0.0238</v>
       </c>
       <c r="J895" t="n">
-        <v>0.4935</v>
+        <v>0.4998</v>
       </c>
     </row>
     <row r="896">
@@ -40029,10 +40029,10 @@
         <v>0.45</v>
       </c>
       <c r="I896" t="n">
-        <v>-1.3421</v>
+        <v>-1.3418</v>
       </c>
       <c r="J896" t="n">
-        <v>-28.1841</v>
+        <v>-28.1778</v>
       </c>
     </row>
     <row r="897">
@@ -41266,13 +41266,13 @@
         <v>20</v>
       </c>
       <c r="H927" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I927" t="n">
-        <v>0.5999</v>
+        <v>0.59</v>
       </c>
       <c r="J927" t="n">
-        <v>11.998</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="928">
@@ -41309,10 +41309,10 @@
         <v>1.27</v>
       </c>
       <c r="I928" t="n">
-        <v>0.3768</v>
+        <v>0.377</v>
       </c>
       <c r="J928" t="n">
-        <v>7.536</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="929">
@@ -41349,10 +41349,10 @@
         <v>1.26</v>
       </c>
       <c r="I929" t="n">
-        <v>0.3656</v>
+        <v>0.3658</v>
       </c>
       <c r="J929" t="n">
-        <v>7.312</v>
+        <v>7.316</v>
       </c>
     </row>
     <row r="930">
@@ -41389,10 +41389,10 @@
         <v>1.14</v>
       </c>
       <c r="I930" t="n">
-        <v>0.2222</v>
+        <v>0.2224</v>
       </c>
       <c r="J930" t="n">
-        <v>4.444</v>
+        <v>4.448</v>
       </c>
     </row>
     <row r="931">
@@ -41429,10 +41429,10 @@
         <v>1.01</v>
       </c>
       <c r="I931" t="n">
-        <v>0.0114</v>
+        <v>0.0115</v>
       </c>
       <c r="J931" t="n">
-        <v>0.228</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="932">
@@ -41869,10 +41869,10 @@
         <v>1.69</v>
       </c>
       <c r="I942" t="n">
-        <v>1.3082</v>
+        <v>1.3089</v>
       </c>
       <c r="J942" t="n">
-        <v>20.9312</v>
+        <v>20.9424</v>
       </c>
     </row>
     <row r="943">
@@ -41906,13 +41906,13 @@
         <v>16</v>
       </c>
       <c r="H943" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I943" t="n">
-        <v>1.1828</v>
+        <v>1.1706</v>
       </c>
       <c r="J943" t="n">
-        <v>18.9248</v>
+        <v>18.7296</v>
       </c>
     </row>
     <row r="944">
@@ -41949,10 +41949,10 @@
         <v>1.46</v>
       </c>
       <c r="I944" t="n">
-        <v>1.0111</v>
+        <v>1.0114</v>
       </c>
       <c r="J944" t="n">
-        <v>16.1776</v>
+        <v>16.1824</v>
       </c>
     </row>
     <row r="945">
@@ -41989,10 +41989,10 @@
         <v>1.36</v>
       </c>
       <c r="I945" t="n">
-        <v>0.8389</v>
+        <v>0.8394</v>
       </c>
       <c r="J945" t="n">
-        <v>13.4224</v>
+        <v>13.4304</v>
       </c>
     </row>
     <row r="946">
@@ -42026,13 +42026,13 @@
         <v>16</v>
       </c>
       <c r="H946" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I946" t="n">
-        <v>0.2461</v>
+        <v>0.2194</v>
       </c>
       <c r="J946" t="n">
-        <v>3.9376</v>
+        <v>3.5104</v>
       </c>
     </row>
     <row r="947">
@@ -42066,13 +42066,13 @@
         <v>16</v>
       </c>
       <c r="H947" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I947" t="n">
-        <v>0.273</v>
+        <v>0.2955</v>
       </c>
       <c r="J947" t="n">
-        <v>4.368</v>
+        <v>4.728</v>
       </c>
     </row>
     <row r="948">
@@ -42109,10 +42109,10 @@
         <v>0.72</v>
       </c>
       <c r="I948" t="n">
-        <v>-0.2984</v>
+        <v>-0.2986</v>
       </c>
       <c r="J948" t="n">
-        <v>-4.7744</v>
+        <v>-4.7776</v>
       </c>
     </row>
     <row r="949">
@@ -42149,10 +42149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I949" t="n">
-        <v>-0.3252</v>
+        <v>-0.3253</v>
       </c>
       <c r="J949" t="n">
-        <v>-5.2032</v>
+        <v>-5.2048</v>
       </c>
     </row>
     <row r="950">
@@ -42189,10 +42189,10 @@
         <v>0.54</v>
       </c>
       <c r="I950" t="n">
-        <v>-0.457</v>
+        <v>-0.4573</v>
       </c>
       <c r="J950" t="n">
-        <v>-7.312</v>
+        <v>-7.3168</v>
       </c>
     </row>
     <row r="951">
@@ -42229,10 +42229,10 @@
         <v>0.42</v>
       </c>
       <c r="I951" t="n">
-        <v>-0.5621</v>
+        <v>-0.5623</v>
       </c>
       <c r="J951" t="n">
-        <v>-8.993600000000001</v>
+        <v>-8.9968</v>
       </c>
     </row>
     <row r="952">
@@ -43066,13 +43066,13 @@
         <v>19</v>
       </c>
       <c r="H972" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I972" t="n">
-        <v>-0.0431</v>
+        <v>-0.0273</v>
       </c>
       <c r="J972" t="n">
-        <v>-0.8189</v>
+        <v>-0.5187</v>
       </c>
     </row>
     <row r="973">
@@ -43109,10 +43109,10 @@
         <v>0.91</v>
       </c>
       <c r="I973" t="n">
-        <v>-0.1225</v>
+        <v>-0.1227</v>
       </c>
       <c r="J973" t="n">
-        <v>-2.3275</v>
+        <v>-2.3313</v>
       </c>
     </row>
     <row r="974">
@@ -43149,10 +43149,10 @@
         <v>0.83</v>
       </c>
       <c r="I974" t="n">
-        <v>-0.2078</v>
+        <v>-0.2079</v>
       </c>
       <c r="J974" t="n">
-        <v>-3.9482</v>
+        <v>-3.9501</v>
       </c>
     </row>
     <row r="975">
@@ -43189,10 +43189,10 @@
         <v>0.8</v>
       </c>
       <c r="I975" t="n">
-        <v>-0.2371</v>
+        <v>-0.2373</v>
       </c>
       <c r="J975" t="n">
-        <v>-4.5049</v>
+        <v>-4.5087</v>
       </c>
     </row>
     <row r="976">
@@ -43229,10 +43229,10 @@
         <v>0.68</v>
       </c>
       <c r="I976" t="n">
-        <v>-0.3501</v>
+        <v>-0.3503</v>
       </c>
       <c r="J976" t="n">
-        <v>-6.6519</v>
+        <v>-6.6557</v>
       </c>
     </row>
     <row r="977">
@@ -43669,10 +43669,10 @@
         <v>1.51</v>
       </c>
       <c r="I987" t="n">
-        <v>0.7088</v>
+        <v>0.7083</v>
       </c>
       <c r="J987" t="n">
-        <v>20.5552</v>
+        <v>20.5407</v>
       </c>
     </row>
     <row r="988">
@@ -43709,10 +43709,10 @@
         <v>1.19</v>
       </c>
       <c r="I988" t="n">
-        <v>0.3225</v>
+        <v>0.3222</v>
       </c>
       <c r="J988" t="n">
-        <v>9.352499999999999</v>
+        <v>9.3438</v>
       </c>
     </row>
     <row r="989">
@@ -43749,10 +43749,10 @@
         <v>0.92</v>
       </c>
       <c r="I989" t="n">
-        <v>-0.1255</v>
+        <v>-0.1256</v>
       </c>
       <c r="J989" t="n">
-        <v>-3.6395</v>
+        <v>-3.6424</v>
       </c>
     </row>
     <row r="990">
@@ -43789,10 +43789,10 @@
         <v>0.84</v>
       </c>
       <c r="I990" t="n">
-        <v>-0.2139</v>
+        <v>-0.2141</v>
       </c>
       <c r="J990" t="n">
-        <v>-6.2031</v>
+        <v>-6.2089</v>
       </c>
     </row>
     <row r="991">
@@ -43826,13 +43826,13 @@
         <v>29</v>
       </c>
       <c r="H991" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="I991" t="n">
-        <v>-0.3949</v>
+        <v>-0.3861</v>
       </c>
       <c r="J991" t="n">
-        <v>-11.4521</v>
+        <v>-11.1969</v>
       </c>
     </row>
     <row r="992">
